--- a/expansion_pack.xlsx
+++ b/expansion_pack.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/strangemax/syncthing/cirfolder/DATASCIENCE FOR HEALTH/Semester 2 /DASC512-202526/Assignment2/git12/512_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/strange-m3/syncthing/cirfolder/DATASCIENCE FOR HEALTH/Semester 2 /DASC512-202526/Assignment2/git12/512_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC54400-91DF-834A-9583-441A1365985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F588F6-58C9-E441-BE9A-E67081939570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="4380" windowWidth="28040" windowHeight="17180" xr2:uid="{BE2FCA61-2DA6-6840-84BA-F08AF7B87FE9}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{BE2FCA61-2DA6-6840-84BA-F08AF7B87FE9}"/>
   </bookViews>
   <sheets>
     <sheet name="expansion_pack" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="532">
   <si>
     <t>report_id</t>
   </si>
@@ -37,60 +37,33 @@
     <t>assigned_label</t>
   </si>
   <si>
-    <t>There is unchanged positioning of a right - sided PICC line near the cavoatrial junction . There is unchanged appearance of mildly decreased lung volumes , with left basilar opacification , most likely atelectasis . There is residual mild enlargement of the cardiomediastinal silhouette , improved since the 05 / 2021 comparison . There is redemonstration of the known anterior mediastinal mass . No focal pulmonary infiltrates are seen . No pleural effusions or pneumothoraces are noted . No acute bony abnormalities are noted .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': [['modify', '2'], ['modify', '5']]}, '2': {'tokens': 'positioning', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': []}, '3': {'tokens': 'right - sided', 'label': 'Anatomy::definitely present', 'start_ix': 6, 'end_ix': 8, 'relations': []}, '4': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 9, 'end_ix': 9, 'relations': [['modify', '5']]}, '5': {'tokens': 'line', 'label': 'Observation::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['located_at', '3']]}, '6': {'tokens': 'cavoatrial junction', 'label': 'Anatomy::definitely present', 'start_ix': 13, 'end_ix': 14, 'relations': []}, '7': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 18, 'end_ix': 18, 'relations': [['modify', '9']]}, '8': {'tokens': 'mildly', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': [['modify', '9']]}, '9': {'tokens': 'decreased', 'label': 'Observation::definitely present', 'start_ix': 22, 'end_ix': 22, 'relations': [['located_at', '10']]}, '10': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': []}, '11': {'tokens': 'volumes', 'label': 'Anatomy::definitely present', 'start_ix': 24, 'end_ix': 24, 'relations': [['modify', '10']]}, '12': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 27, 'end_ix': 27, 'relations': [['modify', '13']]}, '13': {'tokens': 'basilar', 'label': 'Anatomy::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': []}, '14': {'tokens': 'opacification', 'label': 'Observation::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['located_at', '13'], ['suggestive_of', '15']]}, '15': {'tokens': 'atelectasis', 'label': 'Observation::uncertain', 'start_ix': 33, 'end_ix': 33, 'relations': []}, '16': {'tokens': 'mild', 'label': 'Observation::definitely present', 'start_ix': 38, 'end_ix': 38, 'relations': [['modify', '17']]}, '17': {'tokens': 'enlargement', 'label': 'Observation::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': [['located_at', '18']]}, '18': {'tokens': 'cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 42, 'end_ix': 42, 'relations': []}, '19': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['modify', '18']]}, '20': {'tokens': 'improved', 'label': 'Observation::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': [['modify', '17']]}, '21': {'tokens': 'anterior', 'label': 'Anatomy::definitely present', 'start_ix': 59, 'end_ix': 59, 'relations': [['modify', '22']]}, '22': {'tokens': 'mediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 60, 'end_ix': 60, 'relations': []}, '23': {'tokens': 'mass', 'label': 'Observation::definitely present', 'start_ix': 61, 'end_ix': 61, 'relations': [['located_at', '22']]}, '24': {'tokens': 'focal', 'label': 'Observation::definitely absent', 'start_ix': 64, 'end_ix': 64, 'relations': [['modify', '26']]}, '25': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 65, 'end_ix': 65, 'relations': []}, '26': {'tokens': 'infiltrates', 'label': 'Observation::definitely absent', 'start_ix': 66, 'end_ix': 66, 'relations': [['located_at', '25']]}, '27': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 71, 'end_ix': 71, 'relations': []}, '28': {'tokens': 'effusions', 'label': 'Observation::definitely absent', 'start_ix': 72, 'end_ix': 72, 'relations': [['located_at', '27']]}, '29': {'tokens': 'pneumothoraces', 'label': 'Observation::definitely absent', 'start_ix': 74, 'end_ix': 74, 'relations': []}, '30': {'tokens': 'acute', 'label': 'Observation::definitely absent', 'start_ix': 79, 'end_ix': 79, 'relations': [['modify', '32']]}, '31': {'tokens': 'bony', 'label': 'Anatomy::definitely present', 'start_ix': 80, 'end_ix': 80, 'relations': []}, '32': {'tokens': 'abnormalities', 'label': 'Observation::definitely absent', 'start_ix': 81, 'end_ix': 81, 'relations': [['located_at', '31']]}}</t>
   </si>
   <si>
     <t>0.25333333333333335</t>
   </si>
   <si>
-    <t>There is unchanged positioning of a right - sided PICC line near the cavoatrial junction . There is unchanged appearance of mildly decreased lung volumes , with left basilar opacification , most likely atelectasis . There is residual mild enlargement of the cardiomediastinal silhouette , improved since the 9 - 6 - 2010 comparison . There is redemonstration of the known anterior mediastinal mass . No focal pulmonary infiltrates are seen . No pleural effusions or pneumothoraces are noted . No acute bony abnormalities are noted .</t>
-  </si>
-  <si>
-    <t>{'1': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': [['modify', '5']]}, '2': {'tokens': 'positioning', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': [['modify', '1']]}, '3': {'tokens': 'right - sided', 'label': 'Anatomy::definitely present', 'start_ix': 6, 'end_ix': 8, 'relations': []}, '4': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 9, 'end_ix': 9, 'relations': [['modify', '5']]}, '5': {'tokens': 'line', 'label': 'Observation::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['located_at', '6']]}, '6': {'tokens': 'cavoatrial junction', 'label': 'Anatomy::definitely present', 'start_ix': 13, 'end_ix': 14, 'relations': []}, '7': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 18, 'end_ix': 18, 'relations': [['modify', '9']]}, '8': {'tokens': 'mildly', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': [['modify', '9']]}, '9': {'tokens': 'decreased', 'label': 'Observation::definitely present', 'start_ix': 22, 'end_ix': 22, 'relations': [['located_at', '10']]}, '10': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': []}, '11': {'tokens': 'volumes', 'label': 'Anatomy::definitely present', 'start_ix': 24, 'end_ix': 24, 'relations': [['modify', '10']]}, '12': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 27, 'end_ix': 27, 'relations': [['modify', '13']]}, '13': {'tokens': 'basilar', 'label': 'Anatomy::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': []}, '14': {'tokens': 'opacification', 'label': 'Observation::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['located_at', '13'], ['suggestive_of', '15']]}, '15': {'tokens': 'atelectasis', 'label': 'Observation::uncertain', 'start_ix': 33, 'end_ix': 33, 'relations': []}, '16': {'tokens': 'mild', 'label': 'Observation::definitely present', 'start_ix': 38, 'end_ix': 38, 'relations': [['modify', '17']]}, '17': {'tokens': 'enlargement', 'label': 'Observation::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': [['located_at', '18']]}, '18': {'tokens': 'cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 42, 'end_ix': 42, 'relations': []}, '19': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['modify', '18']]}, '20': {'tokens': 'improved', 'label': 'Observation::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': [['modify', '17']]}, '21': {'tokens': 'anterior', 'label': 'Anatomy::definitely present', 'start_ix': 61, 'end_ix': 61, 'relations': [['modify', '22']]}, '22': {'tokens': 'mediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 62, 'end_ix': 62, 'relations': []}, '23': {'tokens': 'mass', 'label': 'Observation::definitely present', 'start_ix': 63, 'end_ix': 63, 'relations': [['located_at', '22']]}, '24': {'tokens': 'focal', 'label': 'Observation::definitely absent', 'start_ix': 66, 'end_ix': 66, 'relations': [['modify', '26']]}, '25': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 67, 'end_ix': 67, 'relations': []}, '26': {'tokens': 'infiltrates', 'label': 'Observation::definitely absent', 'start_ix': 68, 'end_ix': 68, 'relations': [['located_at', '25']]}, '27': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 73, 'end_ix': 73, 'relations': []}, '28': {'tokens': 'effusions', 'label': 'Observation::definitely absent', 'start_ix': 74, 'end_ix': 74, 'relations': [['located_at', '27']]}, '29': {'tokens': 'pneumothoraces', 'label': 'Observation::definitely absent', 'start_ix': 76, 'end_ix': 76, 'relations': []}, '30': {'tokens': 'acute', 'label': 'Observation::definitely absent', 'start_ix': 81, 'end_ix': 81, 'relations': [['modify', '32']]}, '31': {'tokens': 'bony', 'label': 'Anatomy::definitely present', 'start_ix': 82, 'end_ix': 82, 'relations': []}, '32': {'tokens': 'abnormalities', 'label': 'Observation::definitely absent', 'start_ix': 83, 'end_ix': 83, 'relations': [['located_at', '31']]}}</t>
-  </si>
-  <si>
-    <t>Interval placement of NGT / OGT . Interval removal of right arm PICC . Diffuse reticular opacities throughout bilateral lung fields likely reflect a combination of previously seen interlobular septal thickening consistent with moderate pulmonary edema in a background of centrilobular emphysema . No focal consolidations . No pleural effusions . No acute bony abnormalities .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Interval placement', 'label': 'Observation::definitely present', 'start_ix': 0, 'end_ix': 1, 'relations': [['modify', '2'], ['modify', '3']]}, '2': {'tokens': 'NGT', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': []}, '3': {'tokens': 'OGT', 'label': 'Observation::definitely present', 'start_ix': 5, 'end_ix': 5, 'relations': []}, '4': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['modify', '5']]}, '5': {'tokens': 'arm', 'label': 'Anatomy::definitely present', 'start_ix': 11, 'end_ix': 11, 'relations': []}, '6': {'tokens': 'PICC', 'label': 'Observation::definitely absent', 'start_ix': 12, 'end_ix': 12, 'relations': [['located_at', '5']]}, '7': {'tokens': 'Diffuse', 'label': 'Observation::definitely present', 'start_ix': 14, 'end_ix': 14, 'relations': [['modify', '9']]}, '8': {'tokens': 'reticular', 'label': 'Observation::definitely present', 'start_ix': 15, 'end_ix': 15, 'relations': [['modify', '9']]}, '9': {'tokens': 'opacities', 'label': 'Observation::definitely present', 'start_ix': 16, 'end_ix': 16, 'relations': [['located_at', '10'], ['suggestive_of', '16']]}, '10': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '11': {'tokens': 'interlobular', 'label': 'Anatomy::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': []}, '12': {'tokens': 'septal', 'label': 'Anatomy::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': []}, '13': {'tokens': 'thickening', 'label': 'Observation::definitely present', 'start_ix': 30, 'end_ix': 30, 'relations': [['located_at', '12'], ['suggestive_of', '16']]}, '14': {'tokens': 'moderate', 'label': 'Observation::definitely present', 'start_ix': 33, 'end_ix': 33, 'relations': [['modify', '16']]}, '15': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 34, 'end_ix': 34, 'relations': []}, '16': {'tokens': 'edema', 'label': 'Observation::definitely present', 'start_ix': 35, 'end_ix': 35, 'relations': [['located_at', '15']]}, '17': {'tokens': 'centrilobular', 'label': 'Anatomy::definitely present', 'start_ix': 40, 'end_ix': 40, 'relations': []}, '18': {'tokens': 'emphysema', 'label': 'Observation::definitely present', 'start_ix': 41, 'end_ix': 41, 'relations': [['located_at', '17']]}, '19': {'tokens': 'focal consolidations', 'label': 'Observation::definitely absent', 'start_ix': 44, 'end_ix': 45, 'relations': []}, '20': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 48, 'end_ix': 48, 'relations': []}, '21': {'tokens': 'effusions', 'label': 'Observation::definitely absent', 'start_ix': 49, 'end_ix': 49, 'relations': [['located_at', '20']]}, '22': {'tokens': 'acute', 'label': 'Observation::definitely absent', 'start_ix': 52, 'end_ix': 52, 'relations': [['modify', '24']]}, '23': {'tokens': 'bony', 'label': 'Anatomy::definitely present', 'start_ix': 53, 'end_ix': 53, 'relations': []}, '24': {'tokens': 'abnormalities', 'label': 'Observation::definitely absent', 'start_ix': 54, 'end_ix': 54, 'relations': [['located_at', '23']]}}</t>
   </si>
   <si>
-    <t>Left upper extremity PICC is unchanged in position . The cardiomediastinal silhouette is unremarkable . Low lung volumes with vascular crowding . No focal consolidations . No pleural effusions . No acute bony abnormalities .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Left', 'label': 'Anatomy::definitely present', 'start_ix': 0, 'end_ix': 0, 'relations': [['modify', '3']]}, '2': {'tokens': 'upper', 'label': 'Anatomy::definitely present', 'start_ix': 1, 'end_ix': 1, 'relations': [['modify', '3']]}, '3': {'tokens': 'extremity', 'label': 'Anatomy::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': []}, '4': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': [['located_at', '3']]}, '5': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 5, 'end_ix': 5, 'relations': []}, '6': {'tokens': 'cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': []}, '7': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 11, 'end_ix': 11, 'relations': []}, '8': {'tokens': 'unremarkable', 'label': 'Observation::definitely present', 'start_ix': 13, 'end_ix': 13, 'relations': []}, '9': {'tokens': 'Low', 'label': 'Observation::definitely present', 'start_ix': 15, 'end_ix': 15, 'relations': [['located_at', '10'], ['suggestive_of', '13']]}, '10': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 16, 'end_ix': 16, 'relations': []}, '11': {'tokens': 'volumes', 'label': 'Anatomy::definitely present', 'start_ix': 17, 'end_ix': 17, 'relations': [['modify', '10']]}, '12': {'tokens': 'vascular', 'label': 'Anatomy::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '13': {'tokens': 'crowding', 'label': 'Observation::definitely present', 'start_ix': 20, 'end_ix': 20, 'relations': [['located_at', '12']]}, '14': {'tokens': 'focal', 'label': 'Observation::definitely absent', 'start_ix': 23, 'end_ix': 23, 'relations': [['modify', '15']]}, '15': {'tokens': 'consolidations', 'label': 'Observation::definitely absent', 'start_ix': 24, 'end_ix': 24, 'relations': []}, '16': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 27, 'end_ix': 27, 'relations': []}, '17': {'tokens': 'effusions', 'label': 'Observation::definitely absent', 'start_ix': 28, 'end_ix': 28, 'relations': [['located_at', '16']]}, '18': {'tokens': 'acute', 'label': 'Observation::definitely absent', 'start_ix': 31, 'end_ix': 31, 'relations': [['modify', '20']]}, '19': {'tokens': 'bony', 'label': 'Anatomy::definitely present', 'start_ix': 32, 'end_ix': 32, 'relations': []}, '20': {'tokens': 'abnormalities', 'label': 'Observation::definitely absent', 'start_ix': 33, 'end_ix': 33, 'relations': [['located_at', '19']]}}</t>
   </si>
   <si>
-    <t>Right arm PICC terminates in the lower superior vena cava . Postsurgical changes of the right upper lung are again identified . There are Kerley B lines suggestive of pulmonary edema . No evidence of focal consolidation or pleural effusions .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Right arm', 'label': 'Anatomy::definitely present', 'start_ix': 0, 'end_ix': 1, 'relations': []}, '2': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': [['located_at', '1'], ['located_at', '3']]}, '3': {'tokens': 'lower superior vena cava', 'label': 'Anatomy::definitely present', 'start_ix': 6, 'end_ix': 9, 'relations': []}, '4': {'tokens': 'Postsurgical changes', 'label': 'Observation::definitely present', 'start_ix': 11, 'end_ix': 12, 'relations': [['located_at', '5']]}, '5': {'tokens': 'right upper lung', 'label': 'Anatomy::definitely present', 'start_ix': 15, 'end_ix': 17, 'relations': []}, '6': {'tokens': 'Kerley B lines', 'label': 'Observation::definitely present', 'start_ix': 24, 'end_ix': 26, 'relations': [['suggestive_of', '8']]}, '7': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': []}, '8': {'tokens': 'edema', 'label': 'Observation::definitely present', 'start_ix': 30, 'end_ix': 30, 'relations': [['located_at', '7']]}, '9': {'tokens': 'focal consolidation', 'label': 'Observation::definitely absent', 'start_ix': 35, 'end_ix': 36, 'relations': []}, '10': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 38, 'end_ix': 38, 'relations': []}, '11': {'tokens': 'effusions', 'label': 'Observation::definitely absent', 'start_ix': 39, 'end_ix': 39, 'relations': [['located_at', '10']]}}</t>
   </si>
   <si>
     <t>0.26666666666666666</t>
   </si>
   <si>
-    <t>The right internal jugular line has its tip in the top of the right atrium . A PICC line is in similar position . An endotracheal tube is present 4 cm . above the carina . Nasogastric tube is in the stomach . Moderately sized bilateral pleural effusions are present . There is patchy air space consolidation present in both lung bases . There appears to be slight improvement on the right side .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 1, 'end_ix': 1, 'relations': []}, '2': {'tokens': 'internal', 'label': 'Anatomy::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': []}, '3': {'tokens': 'line', 'label': 'Observation::definitely present', 'start_ix': 4, 'end_ix': 4, 'relations': []}, '4': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': [['modify', '3'], ['located_at', '5']]}, '5': {'tokens': 'top', 'label': 'Anatomy::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['modify', '6']]}, '6': {'tokens': 'atrium', 'label': 'Anatomy::definitely present', 'start_ix': 14, 'end_ix': 14, 'relations': []}, '7': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 17, 'end_ix': 18, 'relations': []}, '8': {'tokens': 'similar position', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 22, 'relations': [['modify', '7']]}, '9': {'tokens': 'endotracheal tube', 'label': 'Observation::definitely present', 'start_ix': 25, 'end_ix': 26, 'relations': [['located_at', '10']]}, '10': {'tokens': '4 cm . above', 'label': 'Anatomy::measurement::definitely present', 'start_ix': 29, 'end_ix': 32, 'relations': [['modify', '11']]}, '11': {'tokens': 'carina', 'label': 'Anatomy::definitely present', 'start_ix': 34, 'end_ix': 34, 'relations': []}, '12': {'tokens': 'Nasogastric tube', 'label': 'Observation::definitely present', 'start_ix': 36, 'end_ix': 37, 'relations': [['located_at', '13']]}, '13': {'tokens': 'stomach', 'label': 'Anatomy::definitely present', 'start_ix': 41, 'end_ix': 41, 'relations': []}, '14': {'tokens': 'Moderately sized', 'label': 'Observation::definitely present', 'start_ix': 43, 'end_ix': 44, 'relations': []}, '15': {'tokens': 'sized', 'label': 'Observation::definitely present', 'start_ix': 44, 'end_ix': 44, 'relations': [['modify', '18']]}, '16': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': [['modify', '17']]}, '17': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 46, 'end_ix': 46, 'relations': []}, '18': {'tokens': 'effusions', 'label': 'Observation::definitely present', 'start_ix': 47, 'end_ix': 47, 'relations': [['located_at', '17']]}, '19': {'tokens': 'patchy', 'label': 'Observation::definitely present', 'start_ix': 53, 'end_ix': 53, 'relations': [['modify', '21']]}, '20': {'tokens': 'air space', 'label': 'Observation::definitely present', 'start_ix': 54, 'end_ix': 55, 'relations': [['modify', '21']]}, '21': {'tokens': 'consolidation', 'label': 'Observation::definitely present', 'start_ix': 56, 'end_ix': 56, 'relations': [['located_at', '22']]}, '22': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 60, 'end_ix': 60, 'relations': []}, '23': {'tokens': 'bases', 'label': 'Anatomy::definitely present', 'start_ix': 61, 'end_ix': 61, 'relations': [['modify', '22']]}, '24': {'tokens': 'slight', 'label': 'Observation::definitely present', 'start_ix': 67, 'end_ix': 67, 'relations': [['modify', '25']]}, '25': {'tokens': 'improvement', 'label': 'Observation::definitely present', 'start_ix': 68, 'end_ix': 68, 'relations': [['modify', '21'], ['located_at', '26']]}, '26': {'tokens': 'right side', 'label': 'Anatomy::definitely present', 'start_ix': 71, 'end_ix': 72, 'relations': [['modify', '22']]}}</t>
   </si>
   <si>
     <t>0.2683333333333333</t>
   </si>
   <si>
-    <t>Portable chest shows low lung volumes with crowding of the pulmonary vasculature . A right PICC line is unchanged in its position , terminating 2 . 7 cm below the carina . There is a feeding tube with its tip in the abdomen . Pulmonary edema and left lower lobe atelectasis and bilateral pleural effusions are stable . Otherwise , there is no change from the prior examination .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'low', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': [['located_at', '3']]}, '2': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 4, 'end_ix': 4, 'relations': []}, '3': {'tokens': 'volumes', 'label': 'Anatomy::definitely present', 'start_ix': 5, 'end_ix': 5, 'relations': [['modify', '2']]}, '4': {'tokens': 'crowding', 'label': 'Observation::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': [['located_at', '6']]}, '5': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['modify', '6']]}, '6': {'tokens': 'vasculature', 'label': 'Anatomy::definitely present', 'start_ix': 11, 'end_ix': 11, 'relations': []}, '7': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 14, 'end_ix': 14, 'relations': []}, '8': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 15, 'end_ix': 15, 'relations': [['located_at', '7']]}, '9': {'tokens': 'line', 'label': 'Observation::definitely present', 'start_ix': 16, 'end_ix': 16, 'relations': []}, '10': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 18, 'end_ix': 18, 'relations': []}, '11': {'tokens': 'position', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': [['modify', '10']]}, '12': {'tokens': '2 . 7 cm below', 'label': 'Anatomy::measurement::definitely present', 'start_ix': 24, 'end_ix': 28, 'relations': [['modify', '13']]}, '13': {'tokens': 'carina', 'label': 'Anatomy::definitely present', 'start_ix': 30, 'end_ix': 30, 'relations': []}, '14': {'tokens': 'feeding tube', 'label': 'Observation::definitely present', 'start_ix': 35, 'end_ix': 36, 'relations': []}, '15': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': [['modify', '14'], ['located_at', '16']]}, '16': {'tokens': 'abdomen', 'label': 'Anatomy::definitely present', 'start_ix': 42, 'end_ix': 42, 'relations': []}, '17': {'tokens': 'Pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 44, 'end_ix': 44, 'relations': []}, '18': {'tokens': 'edema', 'label': 'Observation::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': [['located_at', '17']]}, '19': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 47, 'end_ix': 47, 'relations': [['modify', '21']]}, '20': {'tokens': 'lower', 'label': 'Anatomy::definitely present', 'start_ix': 48, 'end_ix': 48, 'relations': [['modify', '21']]}, '21': {'tokens': 'lobe', 'label': 'Anatomy::definitely present', 'start_ix': 49, 'end_ix': 49, 'relations': []}, '22': {'tokens': 'atelectasis', 'label': 'Observation::definitely present', 'start_ix': 50, 'end_ix': 50, 'relations': [['located_at', '21']]}, '23': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 52, 'end_ix': 52, 'relations': [['modify', '24']]}, '24': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 53, 'end_ix': 53, 'relations': []}, '25': {'tokens': 'effusions', 'label': 'Observation::definitely present', 'start_ix': 54, 'end_ix': 54, 'relations': [['located_at', '24']]}, '26': {'tokens': 'stable', 'label': 'Observation::definitely present', 'start_ix': 56, 'end_ix': 56, 'relations': [['modify', '18'], ['modify', '22'], ['modify', '25']]}, '27': {'tokens': 'change', 'label': 'Observation::definitely absent', 'start_ix': 63, 'end_ix': 63, 'relations': []}}</t>
   </si>
   <si>
-    <t>The lower lateral margin of the left hemithorax is excluded from the field - of - view . Grossly stable position of the right arm PICC line given differences in patient positioning . Stable enlarged cardiac silhouette . Interval development of moderate pulmonary edema with bibasilar opacities and small bilateral pleural effusions .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 6, 'end_ix': 6, 'relations': [['modify', '2']]}, '2': {'tokens': 'hemithorax', 'label': 'Anatomy::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': []}, '3': {'tokens': 'stable', 'label': 'Observation::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': [['modify', '7']]}, '4': {'tokens': 'position', 'label': 'Observation::definitely present', 'start_ix': 20, 'end_ix': 20, 'relations': [['modify', '3']]}, '5': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': [['modify', '6']]}, '6': {'tokens': 'arm', 'label': 'Anatomy::definitely present', 'start_ix': 24, 'end_ix': 24, 'relations': []}, '7': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 25, 'end_ix': 26, 'relations': [['located_at', '6']]}, '8': {'tokens': 'Stable', 'label': 'Observation::definitely present', 'start_ix': 33, 'end_ix': 33, 'relations': [['modify', '9']]}, '9': {'tokens': 'enlarged', 'label': 'Observation::definitely present', 'start_ix': 34, 'end_ix': 34, 'relations': [['located_at', '10']]}, '10': {'tokens': 'cardiac', 'label': 'Anatomy::definitely present', 'start_ix': 35, 'end_ix': 35, 'relations': []}, '11': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 36, 'end_ix': 36, 'relations': [['modify', '10']]}, '12': {'tokens': 'moderate', 'label': 'Observation::definitely present', 'start_ix': 41, 'end_ix': 41, 'relations': [['modify', '14']]}, '13': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 42, 'end_ix': 42, 'relations': []}, '14': {'tokens': 'edema', 'label': 'Observation::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['located_at', '13']]}, '15': {'tokens': 'bibasilar', 'label': 'Anatomy::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': []}, '16': {'tokens': 'opacities', 'label': 'Observation::definitely present', 'start_ix': 46, 'end_ix': 46, 'relations': [['located_at', '15']]}, '17': {'tokens': 'small', 'label': 'Observation::definitely present', 'start_ix': 48, 'end_ix': 48, 'relations': [['modify', '20']]}, '18': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 49, 'end_ix': 49, 'relations': [['modify', '19']]}, '19': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 50, 'end_ix': 50, 'relations': []}, '20': {'tokens': 'effusions', 'label': 'Observation::definitely present', 'start_ix': 51, 'end_ix': 51, 'relations': [['located_at', '19']]}}</t>
   </si>
   <si>
@@ -1567,33 +1540,18 @@
     <t>{'1': {'tokens': 'tubes', 'label': 'Observation::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': []}, '2': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 4, 'end_ix': 4, 'relations': [['modify', '1']]}, '3': {'tokens': 'tubes', 'label': 'Observation::definitely present', 'start_ix': 8, 'end_ix': 8, 'relations': []}, '4': {'tokens': 'feeding tube', 'label': 'Observation::definitely present', 'start_ix': 10, 'end_ix': 11, 'relations': []}, '5': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 13, 'end_ix': 13, 'relations': []}, '6': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 14, 'end_ix': 15, 'relations': [['located_at', '5']]}, '7': {'tokens': 'in place', 'label': 'Observation::definitely present', 'start_ix': 16, 'end_ix': 17, 'relations': [['modify', '3'], ['modify', '4'], ['modify', '6']]}, '8': {'tokens': 'Aortic', 'label': 'Anatomy::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '9': {'tokens': 'material', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': []}, '10': {'tokens': 'consolidation', 'label': 'Observation::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': [['located_at', '11']]}, '11': {'tokens': 'left lung base', 'label': 'Anatomy::definitely present', 'start_ix': 31, 'end_ix': 33, 'relations': []}, '12': {'tokens': 'mild opacity', 'label': 'Observation::definitely present', 'start_ix': 37, 'end_ix': 38, 'relations': [['located_at', '13'], ['located_at', '14']]}, '13': {'tokens': 'right lung base', 'label': 'Anatomy::definitely present', 'start_ix': 41, 'end_ix': 43, 'relations': []}, '14': {'tokens': 'right mid - lung', 'label': 'Anatomy::definitely present', 'start_ix': 47, 'end_ix': 50, 'relations': []}, '15': {'tokens': 'pneumothorax', 'label': 'Observation::definitely absent', 'start_ix': 54, 'end_ix': 54, 'relations': []}, '16': {'tokens': 'Multiple', 'label': 'Observation::definitely present', 'start_ix': 58, 'end_ix': 58, 'relations': [['modify', '18']]}, '17': {'tokens': 'right sided rib', 'label': 'Anatomy::definitely present', 'start_ix': 59, 'end_ix': 61, 'relations': []}, '18': {'tokens': 'fractures', 'label': 'Observation::definitely present', 'start_ix': 62, 'end_ix': 62, 'relations': [['located_at', '17']]}}</t>
   </si>
   <si>
-    <t>Left chest tube remains in place as does right PICC line . Persistent small , left apical pneumothorax , not significantly changed in size as compared to prior day ' s study given differences in positioning . Persistent left retrocardiac opacity with associated small , left pleural effusion . There</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Left', 'label': 'Anatomy::definitely present', 'start_ix': 0, 'end_ix': 0, 'relations': [['modify', '2']]}, '2': {'tokens': 'chest', 'label': 'Anatomy::definitely present', 'start_ix': 1, 'end_ix': 1, 'relations': []}, '3': {'tokens': 'tube', 'label': 'Observation::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': [['located_at', '2']]}, '4': {'tokens': 'in place', 'label': 'Observation::definitely present', 'start_ix': 4, 'end_ix': 5, 'relations': [['modify', '3']]}, '5': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 8, 'end_ix': 8, 'relations': []}, '6': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 9, 'end_ix': 9, 'relations': [['modify', '7']]}, '7': {'tokens': 'line', 'label': 'Observation::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['located_at', '5']]}, '8': {'tokens': 'small', 'label': 'Observation::definitely present', 'start_ix': 13, 'end_ix': 13, 'relations': [['modify', '11']]}, '9': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 15, 'end_ix': 15, 'relations': [['modify', '10']]}, '10': {'tokens': 'apical', 'label': 'Anatomy::definitely present', 'start_ix': 16, 'end_ix': 16, 'relations': []}, '11': {'tokens': 'pneumothorax', 'label': 'Observation::definitely present', 'start_ix': 17, 'end_ix': 17, 'relations': [['located_at', '10']]}, '12': {'tokens': 'changed', 'label': 'Observation::definitely absent', 'start_ix': 21, 'end_ix': 21, 'relations': [['modify', '13']]}, '13': {'tokens': 'size', 'label': 'Observation::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': [['modify', '11']]}, '14': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 38, 'end_ix': 38, 'relations': [['modify', '15']]}, '15': {'tokens': 'retrocardiac', 'label': 'Anatomy::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': []}, '16': {'tokens': 'opacity', 'label': 'Observation::definitely present', 'start_ix': 40, 'end_ix': 40, 'relations': [['located_at', '15']]}, '17': {'tokens': 'small', 'label': 'Observation::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['modify', '20']]}, '18': {'tokens': 'left', 'label': 'Anatomy::definitely present', 'start_ix': 45, 'end_ix': 45, 'relations': [['modify', '19']]}, '19': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 46, 'end_ix': 46, 'relations': []}, '20': {'tokens': 'effusion', 'label': 'Observation::definitely present', 'start_ix': 47, 'end_ix': 47, 'relations': [['located_at', '19']]}}</t>
   </si>
   <si>
-    <t>Submitted for review are a series of frontal , portable views of the chest . The first dated April 20 at 15 : 38 demonstrates a right PICC line with its tip in the distal third of the superior vena cava . The cardiomediastinal silhouette is otherwise unremarkable . There is calcification noted of the aortic arch . The lung parenchyma is clear . No pleural , bone , or soft tissue abnormalities noted . Subsequent examination dated 4 - 20 - 2002 at 16 : 34 demonstrates a PICC line with its tip at the cavoatrial junction . There is mildly increased reticular markings with minimally indistinct pulmonary vessels , consistent with mild edema . No other changes are noted .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 26, 'end_ix': 26, 'relations': []}, '2': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 27, 'end_ix': 28, 'relations': [['located_at', '1']]}, '3': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 31, 'end_ix': 31, 'relations': [['modify', '2']]}, '4': {'tokens': 'distal', 'label': 'Anatomy::definitely present', 'start_ix': 34, 'end_ix': 34, 'relations': [['modify', '5']]}, '5': {'tokens': 'third', 'label': 'Anatomy::definitely present', 'start_ix': 35, 'end_ix': 35, 'relations': [['modify', '6']]}, '6': {'tokens': 'superior vena cava', 'label': 'Anatomy::definitely present', 'start_ix': 38, 'end_ix': 40, 'relations': []}, '7': {'tokens': 'cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': []}, '8': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 44, 'end_ix': 44, 'relations': [['modify', '7']]}, '9': {'tokens': 'unremarkable', 'label': 'Observation::definitely present', 'start_ix': 47, 'end_ix': 47, 'relations': [['located_at', '7']]}, '10': {'tokens': 'calcification', 'label': 'Observation::definitely present', 'start_ix': 51, 'end_ix': 51, 'relations': [['located_at', '11']]}, '11': {'tokens': 'aortic arch', 'label': 'Anatomy::definitely present', 'start_ix': 55, 'end_ix': 56, 'relations': []}, '12': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 59, 'end_ix': 59, 'relations': [['modify', '13']]}, '13': {'tokens': 'parenchyma', 'label': 'Anatomy::definitely present', 'start_ix': 60, 'end_ix': 60, 'relations': []}, '14': {'tokens': 'clear', 'label': 'Observation::definitely present', 'start_ix': 62, 'end_ix': 62, 'relations': [['located_at', '13']]}, '15': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 65, 'end_ix': 65, 'relations': []}, '16': {'tokens': 'bone', 'label': 'Anatomy::definitely present', 'start_ix': 67, 'end_ix': 67, 'relations': []}, '17': {'tokens': 'soft tissue', 'label': 'Anatomy::definitely present', 'start_ix': 70, 'end_ix': 71, 'relations': []}, '18': {'tokens': 'abnormalities', 'label': 'Observation::definitely absent', 'start_ix': 72, 'end_ix': 72, 'relations': [['located_at', '15'], ['located_at', '16'], ['located_at', '17']]}, '19': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 89, 'end_ix': 90, 'relations': []}, '20': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 93, 'end_ix': 93, 'relations': [['modify', '19'], ['located_at', '21']]}, '21': {'tokens': 'cavoatrial junction', 'label': 'Anatomy::definitely present', 'start_ix': 96, 'end_ix': 97, 'relations': []}, '22': {'tokens': 'mildly', 'label': 'Observation::definitely present', 'start_ix': 101, 'end_ix': 101, 'relations': [['modify', '23']]}, '23': {'tokens': 'increased', 'label': 'Observation::definitely present', 'start_ix': 102, 'end_ix': 102, 'relations': [['modify', '25']]}, '24': {'tokens': 'reticular', 'label': 'Observation::definitely present', 'start_ix': 103, 'end_ix': 103, 'relations': [['modify', '25']]}, '25': {'tokens': 'markings', 'label': 'Observation::definitely present', 'start_ix': 104, 'end_ix': 104, 'relations': [['suggestive_of', '31']]}, '26': {'tokens': 'minimally', 'label': 'Observation::definitely present', 'start_ix': 106, 'end_ix': 106, 'relations': [['modify', '27']]}, '27': {'tokens': 'indistinct', 'label': 'Observation::definitely present', 'start_ix': 107, 'end_ix': 107, 'relations': [['located_at', '29'], ['suggestive_of', '31']]}, '28': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 108, 'end_ix': 108, 'relations': [['modify', '29']]}, '29': {'tokens': 'vessels', 'label': 'Anatomy::definitely present', 'start_ix': 109, 'end_ix': 109, 'relations': []}, '30': {'tokens': 'mild', 'label': 'Observation::definitely present', 'start_ix': 113, 'end_ix': 113, 'relations': [['modify', '31']]}, '31': {'tokens': 'edema', 'label': 'Observation::uncertain', 'start_ix': 114, 'end_ix': 114, 'relations': []}}</t>
   </si>
   <si>
-    <t>Unchanged positioning of right upper extremity PICC . Interval near resolution of the bilateral diffuse patchy reticular opacities . Bibasilar stranding opacities are consistent with atelectasis . The cardiomediastinal silhouette is normal . Degenerative changes are noted in the thoracic spine .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Unchanged positioning', 'label': 'Observation::definitely present', 'start_ix': 0, 'end_ix': 1, 'relations': []}, '2': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': [['modify', '4']]}, '3': {'tokens': 'upper', 'label': 'Anatomy::definitely present', 'start_ix': 4, 'end_ix': 4, 'relations': [['modify', '4']]}, '4': {'tokens': 'extremity', 'label': 'Anatomy::definitely present', 'start_ix': 5, 'end_ix': 5, 'relations': []}, '5': {'tokens': 'PICC', 'label': 'Observation::definitely present', 'start_ix': 6, 'end_ix': 6, 'relations': [['located_at', '4']]}, '6': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 13, 'end_ix': 13, 'relations': []}, '7': {'tokens': 'diffuse', 'label': 'Observation::definitely present', 'start_ix': 14, 'end_ix': 14, 'relations': [['modify', '10']]}, '8': {'tokens': 'patchy', 'label': 'Observation::definitely present', 'start_ix': 15, 'end_ix': 15, 'relations': [['modify', '10']]}, '9': {'tokens': 'reticular', 'label': 'Observation::definitely present', 'start_ix': 16, 'end_ix': 16, 'relations': [['modify', '10']]}, '10': {'tokens': 'opacities', 'label': 'Observation::definitely present', 'start_ix': 17, 'end_ix': 17, 'relations': [['located_at', '6']]}, '11': {'tokens': 'Bibasilar', 'label': 'Anatomy::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '12': {'tokens': 'stranding', 'label': 'Observation::definitely present', 'start_ix': 20, 'end_ix': 20, 'relations': [['modify', '13']]}, '13': {'tokens': 'opacities', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': [['located_at', '11'], ['suggestive_of', '14']]}, '14': {'tokens': 'atelectasis', 'label': 'Observation::definitely present', 'start_ix': 25, 'end_ix': 25, 'relations': []}, '15': {'tokens': 'cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': []}, '16': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['modify', '15']]}, '17': {'tokens': 'normal', 'label': 'Observation::definitely present', 'start_ix': 31, 'end_ix': 31, 'relations': [['located_at', '15']]}, '18': {'tokens': 'Degenerative', 'label': 'Observation::definitely present', 'start_ix': 33, 'end_ix': 33, 'relations': [['located_at', '19']]}, '19': {'tokens': 'thoracic spine', 'label': 'Anatomy::definitely present', 'start_ix': 39, 'end_ix': 40, 'relations': []}}</t>
   </si>
   <si>
-    <t>Unchanged right pleural effusion . PICC line tip slightly above the expected location of the cavoatrial junction . Partial atelectasis right lower lobe . Cardiomediastinal silhouette unchanged and within normal limits .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'Unchanged', 'label': 'Observation::definitely present', 'start_ix': 0, 'end_ix': 0, 'relations': [['modify', '4']]}, '2': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 1, 'end_ix': 1, 'relations': [['modify', '3']]}, '3': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 2, 'end_ix': 2, 'relations': []}, '4': {'tokens': 'effusion', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': [['located_at', '3']]}, '5': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 5, 'end_ix': 6, 'relations': []}, '6': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': [['modify', '5'], ['located_at', '7']]}, '7': {'tokens': 'cavoatrial junction', 'label': 'Anatomy::definitely present', 'start_ix': 15, 'end_ix': 16, 'relations': []}, '8': {'tokens': 'Partial', 'label': 'Observation::definitely present', 'start_ix': 18, 'end_ix': 18, 'relations': [['modify', '9']]}, '9': {'tokens': 'atelectasis', 'label': 'Observation::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '10': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 20, 'end_ix': 20, 'relations': []}, '11': {'tokens': 'Cardiomediastinal', 'label': 'Anatomy::definitely present', 'start_ix': 24, 'end_ix': 24, 'relations': []}, '12': {'tokens': 'silhouette', 'label': 'Anatomy::definitely present', 'start_ix': 25, 'end_ix': 25, 'relations': [['modify', '11']]}, '13': {'tokens': 'unchanged', 'label': 'Observation::definitely present', 'start_ix': 26, 'end_ix': 26, 'relations': [['located_at', '11']]}, '14': {'tokens': 'normal', 'label': 'Observation::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['located_at', '11']]}, '15': {'tokens': 'limits', 'label': 'Observation::definitely present', 'start_ix': 30, 'end_ix': 30, 'relations': [['modify', '14']]}}</t>
   </si>
   <si>
-    <t>ET tube , NG tube , right IJ Swan - Ganz , right PICC line , 38I CT in place . Significant cardiomegaly with moderate to severe pulmonary edema and left lower lobe areas of atelectasis versus consolidation or aspiration .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'ET tube', 'label': 'Observation::definitely present', 'start_ix': 0, 'end_ix': 1, 'relations': []}, '2': {'tokens': 'NG tube', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 4, 'relations': []}, '3': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 6, 'end_ix': 6, 'relations': [['modify', '4']]}, '4': {'tokens': 'IJ', 'label': 'Anatomy::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': []}, '5': {'tokens': 'Swan - Ganz', 'label': 'Observation::definitely present', 'start_ix': 8, 'end_ix': 10, 'relations': [['located_at', '4']]}, '6': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 12, 'end_ix': 12, 'relations': []}, '7': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 13, 'end_ix': 14, 'relations': [['located_at', '6']]}, '8': {'tokens': 'in place', 'label': 'Observation::definitely present', 'start_ix': 18, 'end_ix': 19, 'relations': [['modify', '1'], ['modify', '7']]}, '9': {'tokens': 'Significant', 'label': 'Observation::definitely present', 'start_ix': 21, 'end_ix': 21, 'relations': [['modify', '10']]}, '10': {'tokens': 'cardiomegaly', 'label': 'Observation::definitely present', 'start_ix': 22, 'end_ix': 22, 'relations': []}, '11': {'tokens': 'moderate to severe', 'label': 'Observation::definitely present', 'start_ix': 24, 'end_ix': 26, 'relations': [['modify', '14']]}, '12': {'tokens': 'severe', 'label': 'Observation::definitely present', 'start_ix': 26, 'end_ix': 26, 'relations': [['modify', '14']]}, '13': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 27, 'end_ix': 27, 'relations': []}, '14': {'tokens': 'edema', 'label': 'Observation::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': [['located_at', '13']]}, '15': {'tokens': 'left lower lobe', 'label': 'Anatomy::definitely present', 'start_ix': 30, 'end_ix': 32, 'relations': []}, '16': {'tokens': 'atelectasis', 'label': 'Observation::definitely present', 'start_ix': 35, 'end_ix': 35, 'relations': [['located_at', '15']]}, '17': {'tokens': 'consolidation', 'label': 'Observation::definitely present', 'start_ix': 37, 'end_ix': 37, 'relations': [['located_at', '15']]}, '18': {'tokens': 'aspiration', 'label': 'Observation::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': [['located_at', '15']]}}</t>
   </si>
   <si>
@@ -1603,23 +1561,385 @@
     <t>{'1': {'tokens': 'Right sided', 'label': 'Anatomy::definitely present', 'start_ix': 0, 'end_ix': 1, 'relations': []}, '2': {'tokens': 'PICC', 'label': 'Observation::definitely absent', 'start_ix': 2, 'end_ix': 2, 'relations': [['modify', '4']]}, '3': {'tokens': 'PICC line', 'label': 'Observation::definitely absent', 'start_ix': 2, 'end_ix': 3, 'relations': []}, '4': {'tokens': 'line', 'label': 'Observation::definitely absent', 'start_ix': 3, 'end_ix': 3, 'relations': [['located_at', '1']]}, '5': {'tokens': 'right sided', 'label': 'Anatomy::definitely present', 'start_ix': 9, 'end_ix': 10, 'relations': []}, '6': {'tokens': 'chest', 'label': 'Observation::definitely absent', 'start_ix': 11, 'end_ix': 11, 'relations': [['modify', '7']]}, '7': {'tokens': 'tube', 'label': 'Observation::definitely absent', 'start_ix': 12, 'end_ix': 12, 'relations': []}, '8': {'tokens': 'pneumothorax', 'label': 'Observation::definitely absent', 'start_ix': 21, 'end_ix': 21, 'relations': []}, '9': {'tokens': 'change', 'label': 'Observation::definitely absent', 'start_ix': 44, 'end_ix': 44, 'relations': []}}</t>
   </si>
   <si>
-    <t>Portable chest shows low lung volumes with crowding of the pulmonary vasculature . There is no change in the right PICC line , enlarged heart and bilateral pleural fluid collections . The bilateral airspace disease has increased with more perihilar and peripheral fluffy opacities worrisome for progression of pneumonia edema or ARDS . Otherwise , there is no change from the prior examination .</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'low', 'label': 'Observation::definitely present', 'start_ix': 3, 'end_ix': 3, 'relations': []}, '2': {'tokens': 'lung', 'label': 'Anatomy::definitely present', 'start_ix': 4, 'end_ix': 4, 'relations': []}, '3': {'tokens': 'volumes', 'label': 'Anatomy::definitely present', 'start_ix': 5, 'end_ix': 5, 'relations': [['modify', '2']]}, '4': {'tokens': 'crowding', 'label': 'Observation::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': [['located_at', '6']]}, '5': {'tokens': 'pulmonary', 'label': 'Anatomy::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['modify', '6']]}, '6': {'tokens': 'vasculature', 'label': 'Anatomy::definitely present', 'start_ix': 11, 'end_ix': 11, 'relations': []}, '7': {'tokens': 'no change', 'label': 'Observation::definitely present', 'start_ix': 15, 'end_ix': 16, 'relations': [['modify', '9']]}, '8': {'tokens': 'right', 'label': 'Anatomy::definitely present', 'start_ix': 19, 'end_ix': 19, 'relations': []}, '9': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 20, 'end_ix': 21, 'relations': [['located_at', '8']]}, '10': {'tokens': 'enlarged', 'label': 'Observation::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': [['located_at', '11']]}, '11': {'tokens': 'heart', 'label': 'Anatomy::definitely present', 'start_ix': 24, 'end_ix': 24, 'relations': []}, '12': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 26, 'end_ix': 26, 'relations': [['modify', '13']]}, '13': {'tokens': 'pleural', 'label': 'Anatomy::definitely present', 'start_ix': 27, 'end_ix': 27, 'relations': []}, '14': {'tokens': 'fluid', 'label': 'Observation::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': [['located_at', '13']]}, '15': {'tokens': 'collections', 'label': 'Observation::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['modify', '14']]}, '16': {'tokens': 'bilateral', 'label': 'Anatomy::definitely present', 'start_ix': 32, 'end_ix': 32, 'relations': [['modify', '17']]}, '17': {'tokens': 'airspace', 'label': 'Anatomy::definitely present', 'start_ix': 33, 'end_ix': 33, 'relations': []}, '18': {'tokens': 'disease', 'label': 'Observation::definitely present', 'start_ix': 34, 'end_ix': 34, 'relations': [['located_at', '17']]}, '19': {'tokens': 'increased', 'label': 'Observation::definitely present', 'start_ix': 36, 'end_ix': 36, 'relations': [['modify', '18']]}, '20': {'tokens': 'perihilar', 'label': 'Anatomy::definitely present', 'start_ix': 39, 'end_ix': 39, 'relations': []}, '21': {'tokens': 'peripheral', 'label': 'Anatomy::definitely present', 'start_ix': 41, 'end_ix': 41, 'relations': []}, '22': {'tokens': 'fluffy', 'label': 'Observation::definitely present', 'start_ix': 42, 'end_ix': 42, 'relations': [['modify', '23']]}, '23': {'tokens': 'opacities', 'label': 'Observation::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['located_at', '20'], ['located_at', '21'], ['suggestive_of', '26']]}, '24': {'tokens': 'pneumonia', 'label': 'Observation::uncertain', 'start_ix': 48, 'end_ix': 48, 'relations': []}, '25': {'tokens': 'edema', 'label': 'Observation::uncertain', 'start_ix': 49, 'end_ix': 49, 'relations': [['modify', '24']]}, '26': {'tokens': 'ARDS', 'label': 'Observation::uncertain', 'start_ix': 51, 'end_ix': 51, 'relations': []}, '27': {'tokens': 'change', 'label': 'Observation::definitely absent', 'start_ix': 58, 'end_ix': 58, 'relations': []}}</t>
   </si>
   <si>
-    <t>Again noted is a right - sided chest tube with small pneumothorax surrounding the chest tube and perhaps at the apex . The apex is somewhat obscured by subcutaneous emphysema . There is a persistent dense opacity over the left hemithorax with the blunting of both costophrenic angles . There is a left - sided PICC line with its tip in the region of the SVC</t>
-  </si>
-  <si>
     <t>{'1': {'tokens': 'right - sided', 'label': 'Anatomy::definitely present', 'start_ix': 4, 'end_ix': 6, 'relations': [['modify', '2']]}, '2': {'tokens': 'chest', 'label': 'Anatomy::definitely present', 'start_ix': 7, 'end_ix': 7, 'relations': []}, '3': {'tokens': 'tube', 'label': 'Observation::definitely present', 'start_ix': 8, 'end_ix': 8, 'relations': [['located_at', '2']]}, '4': {'tokens': 'small', 'label': 'Observation::definitely present', 'start_ix': 10, 'end_ix': 10, 'relations': [['modify', '5']]}, '5': {'tokens': 'pneumothorax', 'label': 'Observation::definitely present', 'start_ix': 11, 'end_ix': 11, 'relations': [['located_at', '7']]}, '6': {'tokens': 'chest', 'label': 'Anatomy::definitely present', 'start_ix': 14, 'end_ix': 14, 'relations': []}, '7': {'tokens': 'apex', 'label': 'Anatomy::definitely present', 'start_ix': 20, 'end_ix': 20, 'relations': []}, '8': {'tokens': 'apex', 'label': 'Anatomy::definitely present', 'start_ix': 23, 'end_ix': 23, 'relations': []}, '9': {'tokens': 'obscured', 'label': 'Observation::definitely present', 'start_ix': 26, 'end_ix': 26, 'relations': [['located_at', '8']]}, '10': {'tokens': 'subcutaneous', 'label': 'Anatomy::definitely present', 'start_ix': 28, 'end_ix': 28, 'relations': []}, '11': {'tokens': 'emphysema', 'label': 'Observation::definitely present', 'start_ix': 29, 'end_ix': 29, 'relations': [['suggestive_of', '9'], ['located_at', '10']]}, '12': {'tokens': 'dense opacity', 'label': 'Observation::definitely present', 'start_ix': 35, 'end_ix': 36, 'relations': [['located_at', '13']]}, '13': {'tokens': 'left hemithorax', 'label': 'Anatomy::definitely present', 'start_ix': 39, 'end_ix': 40, 'relations': []}, '14': {'tokens': 'blunting', 'label': 'Observation::definitely present', 'start_ix': 43, 'end_ix': 43, 'relations': [['located_at', '15']]}, '15': {'tokens': 'costophrenic angles', 'label': 'Anatomy::definitely present', 'start_ix': 46, 'end_ix': 47, 'relations': []}, '16': {'tokens': 'left - sided', 'label': 'Anatomy::definitely present', 'start_ix': 52, 'end_ix': 54, 'relations': []}, '17': {'tokens': 'PICC line', 'label': 'Observation::definitely present', 'start_ix': 55, 'end_ix': 56, 'relations': [['located_at', '16']]}, '18': {'tokens': 'tip', 'label': 'Observation::definitely present', 'start_ix': 59, 'end_ix': 59, 'relations': [['modify', '17'], ['located_at', '19']]}, '19': {'tokens': 'SVC', 'label': 'Anatomy::definitely present', 'start_ix': 65, 'end_ix': 65, 'relations': []}}</t>
+  </si>
+  <si>
+    <t>manual label</t>
+  </si>
+  <si>
+    <r>
+      <t>There is unchanged positioning of a right - sided PICC line near the cavoatrial junction .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> There is unchanged appearance of mildly decreased lung volumes , with left basilar opacification , most likely atelectasis .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> There is residual mild enlargement of the cardiomediastinal silhouette , improved since the 05 / 2021 comparison . There is redemonstration of the known anterior mediastinal mass . No focal pulmonary infiltrates are seen . No pleural effusions or pneumothoraces are noted . No acute bony abnormalities are noted .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Interval placement of NGT / OGT . Interval removal of right arm PICC . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Diffuse reticular opacities throughout bilateral lung fields likely reflect a combination of previously seen interlobular septal thickening consistent with moderate pulmonary edema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in a background of centrilobular emphysema . No focal consolidations . No pleural effusions . No acute bony abnormalities .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Left upper extremity PICC is unchanged in position . The cardiomediastinal silhouette is unremarkable . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Low lung volumes with vascular crowding .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> No focal consolidations . No pleural effusions . No acute bony abnormalities .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Right arm PICC terminates in the lower superior vena cava . Postsurgical changes of the right upper lung are again identified .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> There are Kerley B lines suggestive of pulmonary edema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . No evidence of focal consolidation or pleural effusions .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The right internal jugular line has its tip in the top of the right atrium . A PICC line is in similar position . An endotracheal tube is present 4 cm . above the carina . Nasogastric tube is in the stomach . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">Moderately sized bilateral pleural effusions are present . There is patchy air space consolidation present in both lung bases </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. There appears to be slight improvement on the right side .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Portable chest shows low lung volumes with crowding of the pulmonary vasculature . A right PICC line is unchanged in its position , terminating 2 . 7 cm below the carina . There is a feeding tube with its tip in the abdomen . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Pulmonary edema and left lower lobe atelectasis and bilateral pleural effusions are stable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Otherwise , there is no change from the prior examination .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The lower lateral margin of the left hemithorax is excluded from the field - of - view . Grossly stable position of the right arm PICC line given differences in patient positioning . Stable enlarged cardiac silhouette .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> Interval development of moderate pulmonary edema with bibasilar opacities and small bilateral pleural effusions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Unchanged right pleural effusion . PICC line tip slightly above the expected location of the cavoatrial junction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Partial atelectasis right lower lobe . Cardiomediastinal silhouette unchanged and within normal limits .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Interval removal of left upper extremity PICC line . Normal cardiothymic mediastinal silhouette . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Subtle increase in reticular opacities in the left mid and lower lung zones which is best seen on frontal radiograph and new compared to prior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Again noted is a right - sided chest tube with small pneumothorax surrounding the chest tube and perhaps at the apex . The apex is somewhat obscured by subcutaneous emphysema . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>There is a persistent dense opacity over the left hemithorax with the blunting of both costophrenic angles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . There is a left - sided PICC line with its tip in the region of the SVC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Portable chest shows low lung volumes with crowding of the pulmonary vasculature . There is no change in the right PICC line , enlarged heart and bilateral pleural fluid collections . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>The bilateral airspace disease has increased with more perihilar and peripheral fluffy opacities worrisome for progression of pneumonia edema or ARDS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Otherwise , there is no change from the prior examination .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Unchanged positioning of right upper extremity PICC .</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> Interval near resolution of the bilateral diffuse patchy reticular opacities </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Bibasilar stranding opacities are consistent with atelectasis . The cardiomediastinal silhouette is normal . Degenerative changes are noted in the thoracic spine .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ET tube , NG tube , right IJ Swan - Ganz , right PICC line , 38I CT in place . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Significant cardiomegaly with moderate to severe pulmonary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> edema and left lower lobe areas of atelectasis versus consolidation or aspiration .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unchanged right pleural effusion . PICC line tip slightly above the expected location of the cavoatrial junction . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Partial atelectasis right lower lobe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Cardiomediastinal silhouette unchanged and within normal limits .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Submitted for review are a series of frontal , portable views of the chest . The first dated April 20 at 15 : 38 demonstrates a right PICC line with its tip in the distal third of the superior vena cava . The cardiomediastinal silhouette is otherwise unremarkable . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">There is calcification noted of the aortic arch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. The lung parenchyma is clear . No pleural , bone , or soft tissue abnormalities noted . Subsequent examination dated 4 - 20 - 2002 at 16 : 34 demonstrates a PICC line with its tip at the cavoatrial junction . There is mildly increased reticular markings with minimally indistinct pulmonary vessels , consistent with mild edema . No other changes are noted .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Left chest tube remains in place as does right PICC line . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">Persistent small , left apical pneumothorax </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, not significantly changed in size as compared to prior day ' s study given differences in positioning . Persistent left retrocardiac opacity with associated small , left pleural effusion . There</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1753,6 +2073,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2096,9 +2421,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2474,14 +2802,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC1C81E-3E85-AD49-BB36-527676EDAEBD}">
-  <dimension ref="A1:E301"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F297"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="110" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2493,475 +2825,499 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="85">
       <c r="A2">
         <v>13922</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="51">
+      <c r="A3">
+        <v>53506</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>13924</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3">
+        <v>0.26</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="34">
+      <c r="A4">
+        <v>30642</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D4">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34">
+      <c r="A5">
+        <v>26698</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>53506</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="51">
+      <c r="A6">
+        <v>16666</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>0.26</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>30642</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>30643</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>0.26500000000000001</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="51">
       <c r="A7">
-        <v>30641</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
+        <v>26975</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>521</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>0.26500000000000001</v>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="51">
       <c r="A8">
-        <v>26698</v>
-      </c>
-      <c r="B8" t="s">
+        <v>39013</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="51">
+      <c r="A9">
+        <v>26634</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>16666</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51">
+      <c r="A10">
+        <v>26633</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="68">
+      <c r="A11">
+        <v>30558</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>26975</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51">
+      <c r="A12">
+        <v>41206</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>39013</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51">
+      <c r="A13">
+        <v>57205</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>26634</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="68">
+      <c r="A14">
+        <v>8678</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D12">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>26633</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>30558</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="68">
+      <c r="A15">
+        <v>25823</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>41206</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="34">
       <c r="A16">
-        <v>57205</v>
-      </c>
-      <c r="B16" t="s">
+        <v>57527</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="51">
+      <c r="A17">
+        <v>830</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>8678</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="68">
+      <c r="A18">
+        <v>3429</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>25823</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="68">
+      <c r="A19">
+        <v>6918</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>57527</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="68">
+      <c r="A20">
+        <v>6916</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="68">
+      <c r="A21">
+        <v>39902</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>830</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D21">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="68">
+      <c r="A22">
+        <v>47702</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D22">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="51">
+      <c r="A23">
+        <v>11221</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>3429</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C23" t="s">
         <v>46</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D23">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="51">
+      <c r="A24">
+        <v>3445</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>6918</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C24" t="s">
         <v>48</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D24" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>6916</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="68">
+      <c r="A25">
+        <v>3550</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>39902</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>47702</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="68">
+      <c r="A26">
+        <v>35021</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>53</v>
       </c>
-      <c r="D25">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>11221</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="D26">
+        <v>0.3</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="34">
+      <c r="A27">
+        <v>459</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>55</v>
       </c>
-      <c r="D26">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>3445</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="D27">
+        <v>0.3</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="34">
+      <c r="A28">
+        <v>460</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28">
+        <v>0.3</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="51">
+      <c r="A29">
+        <v>42378</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C29" t="s">
         <v>57</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>3550</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>35021</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" t="s">
-        <v>62</v>
       </c>
       <c r="D29">
         <v>0.3</v>
@@ -2970,15 +3326,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="51">
       <c r="A30">
-        <v>459</v>
-      </c>
-      <c r="B30" t="s">
-        <v>63</v>
+        <v>42379</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>0.3</v>
@@ -2987,15 +3343,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="51">
       <c r="A31">
-        <v>460</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
+        <v>29712</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D31">
         <v>0.3</v>
@@ -3004,15 +3360,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="51">
       <c r="A32">
-        <v>42378</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
+        <v>29703</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D32">
         <v>0.3</v>
@@ -3021,15 +3377,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="68">
       <c r="A33">
-        <v>42379</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
+        <v>35018</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>0.3</v>
@@ -3038,134 +3394,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="51">
       <c r="A34">
-        <v>29712</v>
-      </c>
-      <c r="B34" t="s">
+        <v>9897</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="68">
+      <c r="A35">
+        <v>3549</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="51">
+      <c r="A36">
+        <v>29496</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="34">
+      <c r="A37">
+        <v>15862</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C37" t="s">
         <v>68</v>
       </c>
-      <c r="D34">
-        <v>0.3</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>29703</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35">
-        <v>0.3</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>35018</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36">
-        <v>0.3</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>9897</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="D37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="51">
+      <c r="A38">
+        <v>51059</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="51">
+      <c r="A39">
+        <v>29494</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="51">
+      <c r="A40">
+        <v>5334</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>3549</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C40" t="s">
         <v>72</v>
       </c>
-      <c r="C38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>29496</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D40">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="34">
+      <c r="A41">
+        <v>35820</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C41" t="s">
         <v>74</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>15862</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>51059</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>79</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>75</v>
@@ -3174,15 +3530,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="34">
       <c r="A42">
-        <v>29494</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
+        <v>52083</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>75</v>
@@ -3191,287 +3547,287 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="34">
       <c r="A43">
-        <v>5334</v>
-      </c>
-      <c r="B43" t="s">
+        <v>35817</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="51">
+      <c r="A44">
+        <v>57186</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="51">
+      <c r="A45">
+        <v>18271</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C45" t="s">
         <v>81</v>
       </c>
-      <c r="D43">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>35820</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="D45" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C44" t="s">
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="51">
+      <c r="A46">
+        <v>18269</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="68">
+      <c r="A47">
+        <v>35073</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="C47" t="s">
         <v>84</v>
       </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>52083</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="D47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="68">
+      <c r="A48">
+        <v>17770</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C48" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="51">
+      <c r="A49">
+        <v>17072</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="51">
+      <c r="A50">
+        <v>53149</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="51">
+      <c r="A51">
+        <v>47696</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="51">
+      <c r="A52">
+        <v>53150</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="34">
+      <c r="A53">
+        <v>43734</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="51">
+      <c r="A54">
+        <v>31742</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="68">
+      <c r="A55">
+        <v>35072</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
         <v>84</v>
       </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>35817</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="D55" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C46" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>57186</v>
-      </c>
-      <c r="B47" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>18271</v>
-      </c>
-      <c r="B48" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>18269</v>
-      </c>
-      <c r="B49" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>35073</v>
-      </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>93</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>17770</v>
-      </c>
-      <c r="B51" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>17072</v>
-      </c>
-      <c r="B52" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="68">
+      <c r="A56">
+        <v>17768</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>53149</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C56" t="s">
         <v>98</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D56">
+        <v>0.31</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="34">
+      <c r="A57">
+        <v>36229</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>47696</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C57" t="s">
         <v>100</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D57">
+        <v>0.31</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="51">
+      <c r="A58">
+        <v>50349</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>53150</v>
-      </c>
-      <c r="B55" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>43734</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C58" t="s">
         <v>102</v>
       </c>
-      <c r="C56" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>31742</v>
-      </c>
-      <c r="B57" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>35072</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="s">
-        <v>93</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>91</v>
+      <c r="D58">
+        <v>0.31</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="51">
       <c r="A59">
-        <v>17768</v>
-      </c>
-      <c r="B59" t="s">
-        <v>106</v>
+        <v>50348</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C59" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D59">
         <v>0.31</v>
@@ -3480,236 +3836,236 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="51">
       <c r="A60">
-        <v>36229</v>
-      </c>
-      <c r="B60" t="s">
+        <v>21040</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="51">
+      <c r="A61">
+        <v>28365</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="68">
+      <c r="A62">
+        <v>39840</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C62" t="s">
         <v>109</v>
       </c>
-      <c r="D60">
-        <v>0.31</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>50349</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="D62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="51">
+      <c r="A63">
+        <v>44156</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C63" t="s">
         <v>111</v>
       </c>
-      <c r="D61">
-        <v>0.31</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>50348</v>
-      </c>
-      <c r="B62" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" t="s">
-        <v>111</v>
-      </c>
-      <c r="D62">
-        <v>0.31</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>21040</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="D63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="51">
+      <c r="A64">
+        <v>12922</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>113</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="51">
+      <c r="A65">
+        <v>31059</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>28365</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="C65" t="s">
         <v>115</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="68">
+      <c r="A66">
+        <v>10729</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>39840</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="C66" t="s">
         <v>117</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="68">
+      <c r="A67">
+        <v>39846</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>44156</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="C67" t="s">
         <v>119</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D67" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>12922</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="51">
+      <c r="A68">
+        <v>39118</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>122</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>31059</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="D68" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="68">
+      <c r="A69">
+        <v>14238</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>10729</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="D69" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="51">
+      <c r="A70">
+        <v>80</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>39846</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="D70">
+        <v>0.315</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="51">
+      <c r="A71">
+        <v>12478</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D71">
+        <v>0.315</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="34">
+      <c r="A72">
+        <v>27621</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>39118</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="C72" t="s">
         <v>130</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D72">
+        <v>0.315</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="68">
+      <c r="A73">
+        <v>5825</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>14238</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
         <v>132</v>
-      </c>
-      <c r="C72" t="s">
-        <v>133</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>80</v>
-      </c>
-      <c r="B73" t="s">
-        <v>134</v>
-      </c>
-      <c r="C73" t="s">
-        <v>135</v>
       </c>
       <c r="D73">
         <v>0.315</v>
@@ -3718,15 +4074,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" ht="68">
       <c r="A74">
-        <v>12478</v>
-      </c>
-      <c r="B74" t="s">
-        <v>136</v>
+        <v>5818</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D74">
         <v>0.315</v>
@@ -3735,15 +4091,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="68">
       <c r="A75">
-        <v>27621</v>
-      </c>
-      <c r="B75" t="s">
-        <v>138</v>
+        <v>5827</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D75">
         <v>0.315</v>
@@ -3752,287 +4108,287 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" ht="34">
       <c r="A76">
-        <v>5825</v>
-      </c>
-      <c r="B76" t="s">
+        <v>14884</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="34">
+      <c r="A77">
+        <v>14885</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C77" t="s">
+        <v>136</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="51">
+      <c r="A78">
+        <v>49965</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C78" t="s">
+        <v>139</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="68">
+      <c r="A79">
+        <v>51934</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C79" t="s">
         <v>141</v>
       </c>
-      <c r="D76">
-        <v>0.315</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>5818</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="D79" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="68">
+      <c r="A80">
+        <v>49403</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C80" t="s">
         <v>143</v>
       </c>
-      <c r="D77">
-        <v>0.315</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>5827</v>
-      </c>
-      <c r="B78" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78" t="s">
-        <v>141</v>
-      </c>
-      <c r="D78">
-        <v>0.315</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>14884</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="D80" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="34">
+      <c r="A81">
+        <v>18406</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C81" t="s">
         <v>145</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="68">
+      <c r="A82">
+        <v>12704</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>14885</v>
-      </c>
-      <c r="B80" t="s">
-        <v>144</v>
-      </c>
-      <c r="C80" t="s">
-        <v>145</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>49965</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="C82" t="s">
         <v>147</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D82" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="51">
+      <c r="A83">
+        <v>825</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>51934</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="C83" t="s">
         <v>149</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="51">
+      <c r="A84">
+        <v>39105</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>49403</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="C84" t="s">
         <v>151</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D84" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="51">
+      <c r="A85">
+        <v>41374</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>18406</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="C85" t="s">
         <v>153</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D85" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>12704</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="51">
+      <c r="A86">
+        <v>47394</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C86" t="s">
         <v>156</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>825</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="D86" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="51">
+      <c r="A87">
+        <v>8243</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C87" t="s">
         <v>158</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>39105</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="D87" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="51">
+      <c r="A88">
+        <v>47393</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C88" t="s">
+        <v>156</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="68">
+      <c r="A89">
+        <v>33929</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C89" t="s">
         <v>160</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>41374</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="D89">
+        <v>0.32</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="34">
+      <c r="A90">
+        <v>11028</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C90" t="s">
         <v>162</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D90">
+        <v>0.32</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="51">
+      <c r="A91">
+        <v>10128</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>47394</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="C91" t="s">
         <v>164</v>
       </c>
-      <c r="C89" t="s">
-        <v>165</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>8243</v>
-      </c>
-      <c r="B90" t="s">
-        <v>166</v>
-      </c>
-      <c r="C90" t="s">
-        <v>167</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>47393</v>
-      </c>
-      <c r="B91" t="s">
-        <v>164</v>
-      </c>
-      <c r="C91" t="s">
-        <v>165</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>163</v>
+      <c r="D91">
+        <v>0.32</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" ht="34">
       <c r="A92">
-        <v>33929</v>
-      </c>
-      <c r="B92" t="s">
-        <v>168</v>
+        <v>11031</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C92" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D92">
         <v>0.32</v>
@@ -4041,15 +4397,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" ht="68">
       <c r="A93">
-        <v>11028</v>
-      </c>
-      <c r="B93" t="s">
-        <v>170</v>
+        <v>39888</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D93">
         <v>0.32</v>
@@ -4058,15 +4414,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="51">
       <c r="A94">
-        <v>10128</v>
-      </c>
-      <c r="B94" t="s">
-        <v>172</v>
+        <v>10129</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D94">
         <v>0.32</v>
@@ -4075,15 +4431,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" ht="34">
       <c r="A95">
-        <v>11031</v>
-      </c>
-      <c r="B95" t="s">
-        <v>170</v>
+        <v>9196</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D95">
         <v>0.32</v>
@@ -4092,15 +4448,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" ht="51">
       <c r="A96">
-        <v>39888</v>
-      </c>
-      <c r="B96" t="s">
-        <v>174</v>
+        <v>33932</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="C96" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D96">
         <v>0.32</v>
@@ -4109,15 +4465,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" ht="68">
       <c r="A97">
-        <v>10129</v>
-      </c>
-      <c r="B97" t="s">
+        <v>42385</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" t="s">
         <v>172</v>
-      </c>
-      <c r="C97" t="s">
-        <v>173</v>
       </c>
       <c r="D97">
         <v>0.32</v>
@@ -4126,15 +4482,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" ht="68">
       <c r="A98">
-        <v>9196</v>
-      </c>
-      <c r="B98" t="s">
-        <v>176</v>
+        <v>39891</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="C98" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D98">
         <v>0.32</v>
@@ -4143,304 +4499,304 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" ht="51">
       <c r="A99">
-        <v>33932</v>
-      </c>
-      <c r="B99" t="s">
+        <v>39890</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C99" t="s">
+        <v>174</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="51">
+      <c r="A100">
+        <v>55194</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" t="s">
+        <v>177</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="51">
+      <c r="A101">
+        <v>3708</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C101" t="s">
         <v>179</v>
       </c>
-      <c r="D99">
-        <v>0.32</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>42385</v>
-      </c>
-      <c r="B100" t="s">
+      <c r="D101" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="51">
+      <c r="A102">
+        <v>29254</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C102" t="s">
         <v>181</v>
       </c>
-      <c r="D100">
-        <v>0.32</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>39891</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="D102" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="68">
+      <c r="A103">
+        <v>17107</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C103" t="s">
+        <v>183</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="68">
+      <c r="A104">
+        <v>43311</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C104" t="s">
+        <v>185</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="51">
+      <c r="A105">
+        <v>39889</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C105" t="s">
         <v>174</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D105" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D101">
-        <v>0.32</v>
-      </c>
-      <c r="E101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>39890</v>
-      </c>
-      <c r="B102" t="s">
-        <v>182</v>
-      </c>
-      <c r="C102" t="s">
-        <v>183</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>55194</v>
-      </c>
-      <c r="B103" t="s">
-        <v>185</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="51">
+      <c r="A106">
+        <v>29255</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" t="s">
+        <v>181</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="34">
+      <c r="A107">
+        <v>31424</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104">
-        <v>3708</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="C107" t="s">
         <v>187</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D107" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="34">
+      <c r="A108">
+        <v>31425</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C108" t="s">
+        <v>187</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="51">
+      <c r="A109">
+        <v>6696</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105">
-        <v>29254</v>
-      </c>
-      <c r="B105" t="s">
+      <c r="C109" t="s">
         <v>189</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D109" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106">
-        <v>17107</v>
-      </c>
-      <c r="B106" t="s">
+      <c r="E109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="51">
+      <c r="A110">
+        <v>8528</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C110" t="s">
         <v>192</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107">
-        <v>43311</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="D110" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="51">
+      <c r="A111">
+        <v>38454</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C111" t="s">
         <v>194</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>39889</v>
-      </c>
-      <c r="B108" t="s">
-        <v>182</v>
-      </c>
-      <c r="C108" t="s">
-        <v>183</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>29255</v>
-      </c>
-      <c r="B109" t="s">
-        <v>189</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="D111" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>31424</v>
-      </c>
-      <c r="B110" t="s">
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="68">
+      <c r="A112">
+        <v>16820</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C112" t="s">
         <v>196</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>31425</v>
-      </c>
-      <c r="B111" t="s">
-        <v>195</v>
-      </c>
-      <c r="C111" t="s">
-        <v>196</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>6696</v>
-      </c>
-      <c r="B112" t="s">
+      <c r="D112" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="68">
+      <c r="A113">
+        <v>24362</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C113" t="s">
         <v>198</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D113">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="68">
+      <c r="A114">
+        <v>24364</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C114" t="s">
+        <v>198</v>
+      </c>
+      <c r="D114">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="34">
+      <c r="A115">
+        <v>37928</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>8528</v>
-      </c>
-      <c r="B113" t="s">
+      <c r="C115" t="s">
         <v>200</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D115">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="51">
+      <c r="A116">
+        <v>1214</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>38454</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="C116" t="s">
         <v>202</v>
-      </c>
-      <c r="C114" t="s">
-        <v>203</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>16820</v>
-      </c>
-      <c r="B115" t="s">
-        <v>204</v>
-      </c>
-      <c r="C115" t="s">
-        <v>205</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>24362</v>
-      </c>
-      <c r="B116" t="s">
-        <v>206</v>
-      </c>
-      <c r="C116" t="s">
-        <v>207</v>
       </c>
       <c r="D116">
         <v>0.32500000000000001</v>
@@ -4449,15 +4805,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" ht="51">
       <c r="A117">
-        <v>24364</v>
-      </c>
-      <c r="B117" t="s">
-        <v>206</v>
+        <v>39998</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D117">
         <v>0.32500000000000001</v>
@@ -4466,15 +4822,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" ht="51">
       <c r="A118">
-        <v>37928</v>
-      </c>
-      <c r="B118" t="s">
-        <v>208</v>
+        <v>39999</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C118" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D118">
         <v>0.32500000000000001</v>
@@ -4483,15 +4839,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="68">
       <c r="A119">
-        <v>1214</v>
-      </c>
-      <c r="B119" t="s">
-        <v>210</v>
+        <v>24044</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="C119" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D119">
         <v>0.32500000000000001</v>
@@ -4500,389 +4856,389 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" ht="34">
       <c r="A120">
-        <v>39998</v>
-      </c>
-      <c r="B120" t="s">
+        <v>23538</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C120" t="s">
+        <v>208</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="51">
+      <c r="A121">
+        <v>18350</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C121" t="s">
+        <v>211</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="34">
+      <c r="A122">
+        <v>22634</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C122" t="s">
         <v>213</v>
       </c>
-      <c r="D120">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>39999</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
-      </c>
-      <c r="C121" t="s">
-        <v>213</v>
-      </c>
-      <c r="D121">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>24044</v>
-      </c>
-      <c r="B122" t="s">
+      <c r="D122" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="68">
+      <c r="A123">
+        <v>46408</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>215</v>
       </c>
-      <c r="D122">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>23538</v>
-      </c>
-      <c r="B123" t="s">
+      <c r="D123" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="68">
+      <c r="A124">
+        <v>38604</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C124" t="s">
         <v>217</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D124" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="34">
+      <c r="A125">
+        <v>32131</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>18350</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="C125" t="s">
         <v>219</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D125" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="51">
+      <c r="A126">
+        <v>37843</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C126" t="s">
+        <v>222</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="51">
+      <c r="A127">
+        <v>26953</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C127" t="s">
+        <v>224</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="68">
+      <c r="A128">
+        <v>53117</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C128" t="s">
+        <v>226</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="51">
+      <c r="A129">
+        <v>26952</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="34">
+      <c r="A130">
+        <v>38468</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C130" t="s">
+        <v>228</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="51">
+      <c r="A131">
+        <v>19260</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C131" t="s">
+        <v>230</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="51">
+      <c r="A132">
+        <v>20490</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C132" t="s">
+        <v>232</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="51">
+      <c r="A133">
+        <v>9195</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C133" t="s">
+        <v>234</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="51">
+      <c r="A134">
+        <v>19035</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C134" t="s">
+        <v>236</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="68">
+      <c r="A135">
+        <v>52434</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C135" t="s">
+        <v>238</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="51">
+      <c r="A136">
+        <v>19036</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" t="s">
+        <v>236</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="51">
+      <c r="A137">
+        <v>19262</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C137" t="s">
+        <v>230</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="34">
+      <c r="A138">
+        <v>32130</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>22634</v>
-      </c>
-      <c r="B125" t="s">
-        <v>221</v>
-      </c>
-      <c r="C125" t="s">
-        <v>222</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>46408</v>
-      </c>
-      <c r="B126" t="s">
-        <v>223</v>
-      </c>
-      <c r="C126" t="s">
-        <v>224</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>38604</v>
-      </c>
-      <c r="B127" t="s">
-        <v>225</v>
-      </c>
-      <c r="C127" t="s">
-        <v>226</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>32131</v>
-      </c>
-      <c r="B128" t="s">
-        <v>227</v>
-      </c>
-      <c r="C128" t="s">
-        <v>228</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>37843</v>
-      </c>
-      <c r="B129" t="s">
-        <v>230</v>
-      </c>
-      <c r="C129" t="s">
-        <v>231</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>26953</v>
-      </c>
-      <c r="B130" t="s">
-        <v>232</v>
-      </c>
-      <c r="C130" t="s">
-        <v>233</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>53117</v>
-      </c>
-      <c r="B131" t="s">
-        <v>234</v>
-      </c>
-      <c r="C131" t="s">
-        <v>235</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>26952</v>
-      </c>
-      <c r="B132" t="s">
-        <v>232</v>
-      </c>
-      <c r="C132" t="s">
-        <v>233</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>38468</v>
-      </c>
-      <c r="B133" t="s">
-        <v>236</v>
-      </c>
-      <c r="C133" t="s">
-        <v>237</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>19260</v>
-      </c>
-      <c r="B134" t="s">
-        <v>238</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="C138" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="51">
+      <c r="A139">
+        <v>4394</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>20490</v>
-      </c>
-      <c r="B135" t="s">
+      <c r="C139" t="s">
         <v>240</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D139">
+        <v>0.33</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="68">
+      <c r="A140">
+        <v>54942</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>9195</v>
-      </c>
-      <c r="B136" t="s">
+      <c r="C140" t="s">
         <v>242</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D140">
+        <v>0.33</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="51">
+      <c r="A141">
+        <v>39114</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>19035</v>
-      </c>
-      <c r="B137" t="s">
+      <c r="C141" t="s">
         <v>244</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D141">
+        <v>0.33</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="34">
+      <c r="A142">
+        <v>11088</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>52434</v>
-      </c>
-      <c r="B138" t="s">
+      <c r="C142" t="s">
         <v>246</v>
-      </c>
-      <c r="C138" t="s">
-        <v>247</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>19036</v>
-      </c>
-      <c r="B139" t="s">
-        <v>244</v>
-      </c>
-      <c r="C139" t="s">
-        <v>245</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>19262</v>
-      </c>
-      <c r="B140" t="s">
-        <v>238</v>
-      </c>
-      <c r="C140" t="s">
-        <v>239</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>32130</v>
-      </c>
-      <c r="B141" t="s">
-        <v>227</v>
-      </c>
-      <c r="C141" t="s">
-        <v>228</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>4394</v>
-      </c>
-      <c r="B142" t="s">
-        <v>248</v>
-      </c>
-      <c r="C142" t="s">
-        <v>249</v>
       </c>
       <c r="D142">
         <v>0.33</v>
@@ -4891,15 +5247,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" ht="51">
       <c r="A143">
-        <v>54942</v>
-      </c>
-      <c r="B143" t="s">
-        <v>250</v>
+        <v>21417</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="C143" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D143">
         <v>0.33</v>
@@ -4908,15 +5264,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="51">
       <c r="A144">
-        <v>39114</v>
-      </c>
-      <c r="B144" t="s">
-        <v>252</v>
+        <v>27685</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="C144" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D144">
         <v>0.33</v>
@@ -4925,15 +5281,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="51">
       <c r="A145">
-        <v>11088</v>
-      </c>
-      <c r="B145" t="s">
-        <v>254</v>
+        <v>35609</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C145" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D145">
         <v>0.33</v>
@@ -4942,15 +5298,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="51">
       <c r="A146">
-        <v>21417</v>
-      </c>
-      <c r="B146" t="s">
-        <v>256</v>
+        <v>1744</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="C146" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D146">
         <v>0.33</v>
@@ -4959,15 +5315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" ht="68">
       <c r="A147">
-        <v>27685</v>
-      </c>
-      <c r="B147" t="s">
-        <v>258</v>
+        <v>39884</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D147">
         <v>0.33</v>
@@ -4976,15 +5332,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" ht="34">
       <c r="A148">
-        <v>35609</v>
-      </c>
-      <c r="B148" t="s">
-        <v>260</v>
+        <v>12269</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D148">
         <v>0.33</v>
@@ -4993,66 +5349,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" ht="85">
       <c r="A149">
-        <v>1744</v>
-      </c>
-      <c r="B149" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C149" t="s">
+        <v>260</v>
+      </c>
+      <c r="D149">
+        <v>0.5</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="34">
+      <c r="A150">
+        <v>6582</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C150" t="s">
         <v>262</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D150">
+        <v>0.5</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="68">
+      <c r="A151">
+        <v>13410</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D149">
-        <v>0.33</v>
-      </c>
-      <c r="E149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>39884</v>
-      </c>
-      <c r="B150" t="s">
+      <c r="C151" t="s">
         <v>264</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D151">
+        <v>0.5</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="34">
+      <c r="A152">
+        <v>15960</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D150">
-        <v>0.33</v>
-      </c>
-      <c r="E150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>12269</v>
-      </c>
-      <c r="B151" t="s">
+      <c r="C152" t="s">
         <v>266</v>
-      </c>
-      <c r="C151" t="s">
-        <v>267</v>
-      </c>
-      <c r="D151">
-        <v>0.33</v>
-      </c>
-      <c r="E151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>3092</v>
-      </c>
-      <c r="B152" t="s">
-        <v>268</v>
-      </c>
-      <c r="C152" t="s">
-        <v>269</v>
       </c>
       <c r="D152">
         <v>0.5</v>
@@ -5061,15 +5417,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" ht="68">
       <c r="A153">
-        <v>6582</v>
-      </c>
-      <c r="B153" t="s">
-        <v>270</v>
+        <v>24512</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="C153" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D153">
         <v>0.5</v>
@@ -5078,15 +5434,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" ht="34">
       <c r="A154">
-        <v>13410</v>
-      </c>
-      <c r="B154" t="s">
-        <v>272</v>
+        <v>52753</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="C154" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D154">
         <v>0.5</v>
@@ -5095,15 +5451,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" ht="102">
       <c r="A155">
-        <v>15960</v>
-      </c>
-      <c r="B155" t="s">
-        <v>274</v>
+        <v>35384</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="C155" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D155">
         <v>0.5</v>
@@ -5112,15 +5468,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" ht="68">
       <c r="A156">
-        <v>24512</v>
-      </c>
-      <c r="B156" t="s">
-        <v>276</v>
+        <v>24511</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="C156" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D156">
         <v>0.5</v>
@@ -5129,15 +5485,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" ht="51">
       <c r="A157">
-        <v>52753</v>
-      </c>
-      <c r="B157" t="s">
-        <v>278</v>
+        <v>33644</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="C157" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D157">
         <v>0.5</v>
@@ -5146,15 +5502,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" ht="51">
       <c r="A158">
-        <v>35384</v>
-      </c>
-      <c r="B158" t="s">
-        <v>280</v>
+        <v>7149</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="C158" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D158">
         <v>0.5</v>
@@ -5163,15 +5519,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" ht="51">
       <c r="A159">
-        <v>24511</v>
-      </c>
-      <c r="B159" t="s">
-        <v>276</v>
+        <v>48869</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="C159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D159">
         <v>0.5</v>
@@ -5180,15 +5536,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="51">
       <c r="A160">
-        <v>33644</v>
-      </c>
-      <c r="B160" t="s">
-        <v>282</v>
+        <v>369</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="C160" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D160">
         <v>0.5</v>
@@ -5197,15 +5553,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" ht="51">
       <c r="A161">
-        <v>7149</v>
-      </c>
-      <c r="B161" t="s">
-        <v>284</v>
+        <v>19362</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="C161" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D161">
         <v>0.5</v>
@@ -5214,15 +5570,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" ht="34">
       <c r="A162">
-        <v>48869</v>
-      </c>
-      <c r="B162" t="s">
-        <v>286</v>
+        <v>20346</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="C162" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D162">
         <v>0.5</v>
@@ -5231,15 +5587,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" ht="119">
       <c r="A163">
-        <v>369</v>
-      </c>
-      <c r="B163" t="s">
-        <v>288</v>
+        <v>36912</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="C163" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D163">
         <v>0.5</v>
@@ -5248,15 +5604,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" ht="34">
       <c r="A164">
-        <v>19362</v>
-      </c>
-      <c r="B164" t="s">
-        <v>290</v>
+        <v>9825</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="C164" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D164">
         <v>0.5</v>
@@ -5265,15 +5621,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" ht="51">
       <c r="A165">
-        <v>20346</v>
-      </c>
-      <c r="B165" t="s">
-        <v>292</v>
+        <v>41197</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="C165" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D165">
         <v>0.5</v>
@@ -5282,15 +5638,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" ht="51">
       <c r="A166">
-        <v>36912</v>
-      </c>
-      <c r="B166" t="s">
-        <v>294</v>
+        <v>37524</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="C166" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D166">
         <v>0.5</v>
@@ -5299,15 +5655,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" ht="51">
       <c r="A167">
-        <v>9825</v>
-      </c>
-      <c r="B167" t="s">
-        <v>296</v>
+        <v>5438</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="C167" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D167">
         <v>0.5</v>
@@ -5316,15 +5672,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" ht="51">
       <c r="A168">
-        <v>41197</v>
-      </c>
-      <c r="B168" t="s">
-        <v>298</v>
+        <v>25934</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="C168" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D168">
         <v>0.5</v>
@@ -5333,15 +5689,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" ht="34">
       <c r="A169">
-        <v>37524</v>
-      </c>
-      <c r="B169" t="s">
-        <v>300</v>
+        <v>48687</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="C169" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D169">
         <v>0.5</v>
@@ -5350,15 +5706,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" ht="34">
       <c r="A170">
-        <v>5438</v>
-      </c>
-      <c r="B170" t="s">
-        <v>302</v>
+        <v>14190</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="C170" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D170">
         <v>0.5</v>
@@ -5367,15 +5723,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" ht="136">
       <c r="A171">
-        <v>25934</v>
-      </c>
-      <c r="B171" t="s">
-        <v>304</v>
+        <v>730</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="C171" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D171">
         <v>0.5</v>
@@ -5384,15 +5740,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" ht="51">
       <c r="A172">
-        <v>48687</v>
-      </c>
-      <c r="B172" t="s">
-        <v>306</v>
+        <v>11428</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="C172" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D172">
         <v>0.5</v>
@@ -5401,15 +5757,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" ht="51">
       <c r="A173">
-        <v>14190</v>
-      </c>
-      <c r="B173" t="s">
-        <v>308</v>
+        <v>11427</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="C173" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D173">
         <v>0.5</v>
@@ -5418,15 +5774,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" ht="51">
       <c r="A174">
-        <v>730</v>
-      </c>
-      <c r="B174" t="s">
-        <v>310</v>
+        <v>10090</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="C174" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D174">
         <v>0.5</v>
@@ -5435,15 +5791,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" ht="17">
       <c r="A175">
-        <v>11428</v>
-      </c>
-      <c r="B175" t="s">
-        <v>312</v>
+        <v>46278</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="C175" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D175">
         <v>0.5</v>
@@ -5452,15 +5808,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" ht="34">
       <c r="A176">
-        <v>11427</v>
-      </c>
-      <c r="B176" t="s">
-        <v>312</v>
+        <v>16922</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="C176" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D176">
         <v>0.5</v>
@@ -5469,15 +5825,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" ht="85">
       <c r="A177">
-        <v>10090</v>
-      </c>
-      <c r="B177" t="s">
-        <v>314</v>
+        <v>47151</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="C177" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D177">
         <v>0.5</v>
@@ -5486,15 +5842,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" ht="51">
       <c r="A178">
-        <v>46278</v>
-      </c>
-      <c r="B178" t="s">
-        <v>316</v>
+        <v>29354</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>313</v>
       </c>
       <c r="C178" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D178">
         <v>0.5</v>
@@ -5503,15 +5859,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" ht="51">
       <c r="A179">
-        <v>16922</v>
-      </c>
-      <c r="B179" t="s">
-        <v>318</v>
+        <v>11398</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="C179" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D179">
         <v>0.5</v>
@@ -5520,15 +5876,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" ht="68">
       <c r="A180">
-        <v>47151</v>
-      </c>
-      <c r="B180" t="s">
-        <v>320</v>
+        <v>18913</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="C180" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D180">
         <v>0.5</v>
@@ -5537,15 +5893,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" ht="51">
       <c r="A181">
-        <v>29354</v>
-      </c>
-      <c r="B181" t="s">
-        <v>322</v>
+        <v>45103</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="C181" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D181">
         <v>0.5</v>
@@ -5554,15 +5910,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" ht="102">
       <c r="A182">
-        <v>11398</v>
-      </c>
-      <c r="B182" t="s">
-        <v>324</v>
+        <v>27306</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="C182" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D182">
         <v>0.5</v>
@@ -5571,15 +5927,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" ht="102">
       <c r="A183">
-        <v>18913</v>
-      </c>
-      <c r="B183" t="s">
-        <v>326</v>
+        <v>27305</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>323</v>
       </c>
       <c r="C183" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D183">
         <v>0.5</v>
@@ -5588,15 +5944,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" ht="34">
       <c r="A184">
-        <v>45103</v>
-      </c>
-      <c r="B184" t="s">
-        <v>328</v>
+        <v>33261</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="C184" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D184">
         <v>0.5</v>
@@ -5605,15 +5961,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" ht="34">
       <c r="A185">
-        <v>27306</v>
-      </c>
-      <c r="B185" t="s">
-        <v>330</v>
+        <v>9456</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="C185" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D185">
         <v>0.5</v>
@@ -5622,15 +5978,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" ht="34">
       <c r="A186">
-        <v>27305</v>
-      </c>
-      <c r="B186" t="s">
-        <v>332</v>
+        <v>27295</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="C186" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D186">
         <v>0.5</v>
@@ -5639,15 +5995,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" ht="34">
       <c r="A187">
-        <v>33261</v>
-      </c>
-      <c r="B187" t="s">
-        <v>334</v>
+        <v>27294</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="C187" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D187">
         <v>0.5</v>
@@ -5656,15 +6012,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" ht="85">
       <c r="A188">
-        <v>9456</v>
-      </c>
-      <c r="B188" t="s">
-        <v>336</v>
+        <v>1394</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="C188" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D188">
         <v>0.5</v>
@@ -5673,15 +6029,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" ht="51">
       <c r="A189">
-        <v>27295</v>
-      </c>
-      <c r="B189" t="s">
-        <v>338</v>
+        <v>37059</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C189" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D189">
         <v>0.5</v>
@@ -5690,15 +6046,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" ht="34">
       <c r="A190">
-        <v>27294</v>
-      </c>
-      <c r="B190" t="s">
-        <v>338</v>
+        <v>6110</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C190" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D190">
         <v>0.5</v>
@@ -5707,15 +6063,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" ht="51">
       <c r="A191">
-        <v>1394</v>
-      </c>
-      <c r="B191" t="s">
-        <v>340</v>
+        <v>44489</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C191" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D191">
         <v>0.5</v>
@@ -5724,15 +6080,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" ht="102">
       <c r="A192">
-        <v>37059</v>
-      </c>
-      <c r="B192" t="s">
-        <v>342</v>
+        <v>35552</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="C192" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D192">
         <v>0.5</v>
@@ -5741,15 +6097,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" ht="51">
       <c r="A193">
-        <v>6110</v>
-      </c>
-      <c r="B193" t="s">
-        <v>344</v>
+        <v>19363</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="C193" t="s">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="D193">
         <v>0.5</v>
@@ -5758,15 +6114,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" ht="34">
       <c r="A194">
-        <v>44489</v>
-      </c>
-      <c r="B194" t="s">
-        <v>346</v>
+        <v>1597</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="C194" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D194">
         <v>0.5</v>
@@ -5775,15 +6131,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" ht="51">
       <c r="A195">
-        <v>35552</v>
-      </c>
-      <c r="B195" t="s">
-        <v>348</v>
+        <v>29247</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C195" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D195">
         <v>0.5</v>
@@ -5792,15 +6148,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" ht="34">
       <c r="A196">
-        <v>19363</v>
-      </c>
-      <c r="B196" t="s">
-        <v>290</v>
+        <v>50631</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C196" t="s">
-        <v>291</v>
+        <v>346</v>
       </c>
       <c r="D196">
         <v>0.5</v>
@@ -5809,15 +6165,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" ht="51">
       <c r="A197">
-        <v>1597</v>
-      </c>
-      <c r="B197" t="s">
-        <v>350</v>
+        <v>29249</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C197" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D197">
         <v>0.5</v>
@@ -5826,15 +6182,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" ht="68">
       <c r="A198">
-        <v>29247</v>
-      </c>
-      <c r="B198" t="s">
-        <v>352</v>
+        <v>20491</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="C198" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D198">
         <v>0.5</v>
@@ -5843,15 +6199,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" ht="68">
       <c r="A199">
-        <v>50631</v>
-      </c>
-      <c r="B199" t="s">
-        <v>354</v>
+        <v>17766</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="C199" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D199">
         <v>0.5</v>
@@ -5860,15 +6216,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" ht="34">
       <c r="A200">
-        <v>29249</v>
-      </c>
-      <c r="B200" t="s">
+        <v>7774</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C200" t="s">
         <v>352</v>
-      </c>
-      <c r="C200" t="s">
-        <v>353</v>
       </c>
       <c r="D200">
         <v>0.5</v>
@@ -5877,15 +6233,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" ht="119">
       <c r="A201">
-        <v>20491</v>
-      </c>
-      <c r="B201" t="s">
-        <v>356</v>
+        <v>12169</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="C201" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D201">
         <v>0.5</v>
@@ -5894,15 +6250,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" ht="51">
       <c r="A202">
-        <v>17766</v>
-      </c>
-      <c r="B202" t="s">
-        <v>358</v>
+        <v>11057</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="C202" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D202">
         <v>0.5</v>
@@ -5911,15 +6267,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" ht="34">
       <c r="A203">
-        <v>7774</v>
-      </c>
-      <c r="B203" t="s">
-        <v>360</v>
+        <v>9868</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="C203" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D203">
         <v>0.5</v>
@@ -5928,15 +6284,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" ht="51">
       <c r="A204">
-        <v>12169</v>
-      </c>
-      <c r="B204" t="s">
-        <v>362</v>
+        <v>10477</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="C204" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D204">
         <v>0.5</v>
@@ -5945,15 +6301,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" ht="51">
       <c r="A205">
-        <v>11057</v>
-      </c>
-      <c r="B205" t="s">
-        <v>364</v>
+        <v>37271</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="C205" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D205">
         <v>0.5</v>
@@ -5962,15 +6318,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" ht="68">
       <c r="A206">
-        <v>9868</v>
-      </c>
-      <c r="B206" t="s">
-        <v>366</v>
+        <v>8886</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="C206" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D206">
         <v>0.5</v>
@@ -5979,15 +6335,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" ht="51">
       <c r="A207">
-        <v>10477</v>
-      </c>
-      <c r="B207" t="s">
-        <v>368</v>
+        <v>21380</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="C207" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D207">
         <v>0.5</v>
@@ -5996,15 +6352,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" ht="34">
       <c r="A208">
-        <v>37271</v>
-      </c>
-      <c r="B208" t="s">
-        <v>370</v>
+        <v>27813</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="C208" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D208">
         <v>0.5</v>
@@ -6013,15 +6369,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" ht="51">
       <c r="A209">
-        <v>8886</v>
-      </c>
-      <c r="B209" t="s">
-        <v>372</v>
+        <v>20423</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="C209" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D209">
         <v>0.5</v>
@@ -6030,15 +6386,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" ht="51">
       <c r="A210">
-        <v>21380</v>
-      </c>
-      <c r="B210" t="s">
-        <v>374</v>
+        <v>45104</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="C210" t="s">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="D210">
         <v>0.5</v>
@@ -6047,15 +6403,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" ht="51">
       <c r="A211">
-        <v>27813</v>
-      </c>
-      <c r="B211" t="s">
-        <v>376</v>
+        <v>19270</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="C211" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D211">
         <v>0.5</v>
@@ -6064,1537 +6420,1572 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" ht="34">
       <c r="A212">
-        <v>20423</v>
-      </c>
-      <c r="B212" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C212" t="s">
+        <v>374</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="51">
+      <c r="A213">
+        <v>35107</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C213" t="s">
+        <v>377</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="34">
+      <c r="A214">
+        <v>24370</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C214" t="s">
         <v>379</v>
       </c>
-      <c r="D212">
-        <v>0.5</v>
-      </c>
-      <c r="E212">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>45104</v>
-      </c>
-      <c r="B213" t="s">
-        <v>328</v>
-      </c>
-      <c r="C213" t="s">
-        <v>329</v>
-      </c>
-      <c r="D213">
-        <v>0.5</v>
-      </c>
-      <c r="E213">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>19270</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="D214" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="51">
+      <c r="A215">
+        <v>39583</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C215" t="s">
         <v>381</v>
       </c>
-      <c r="D214">
-        <v>0.5</v>
-      </c>
-      <c r="E214">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>2420</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="D215" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="51">
+      <c r="A216">
+        <v>5610</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C216" t="s">
         <v>383</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D216" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="68">
+      <c r="A217">
+        <v>49646</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E215">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>35107</v>
-      </c>
-      <c r="B216" t="s">
+      <c r="C217" t="s">
         <v>385</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D217" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="68">
+      <c r="A218">
+        <v>7380</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E216">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>24370</v>
-      </c>
-      <c r="B217" t="s">
+      <c r="C218" t="s">
         <v>387</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D218" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="34">
+      <c r="A219">
+        <v>47585</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E217">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>39583</v>
-      </c>
-      <c r="B218" t="s">
+      <c r="C219" t="s">
         <v>389</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D219" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="68">
+      <c r="A220">
+        <v>7381</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C220" t="s">
+        <v>387</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="34">
+      <c r="A221">
+        <v>10478</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D218" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E218">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A219">
-        <v>5610</v>
-      </c>
-      <c r="B219" t="s">
+      <c r="C221" t="s">
         <v>391</v>
       </c>
-      <c r="C219" t="s">
+      <c r="D221" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="34">
+      <c r="A222">
+        <v>24371</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C222" t="s">
+        <v>379</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="68">
+      <c r="A223">
+        <v>7382</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C223" t="s">
+        <v>387</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="51">
+      <c r="A224">
+        <v>53471</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E219">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A220">
-        <v>49646</v>
-      </c>
-      <c r="B220" t="s">
+      <c r="C224" t="s">
         <v>393</v>
       </c>
-      <c r="C220" t="s">
+      <c r="D224" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="34">
+      <c r="A225">
+        <v>17790</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E220">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>7380</v>
-      </c>
-      <c r="B221" t="s">
+      <c r="C225" t="s">
         <v>395</v>
       </c>
-      <c r="C221" t="s">
+      <c r="D225" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="34">
+      <c r="A226">
+        <v>10613</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E221">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>47585</v>
-      </c>
-      <c r="B222" t="s">
+      <c r="C226" t="s">
         <v>397</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D226" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="34">
+      <c r="A227">
+        <v>38864</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E222">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A223">
-        <v>7381</v>
-      </c>
-      <c r="B223" t="s">
-        <v>395</v>
-      </c>
-      <c r="C223" t="s">
-        <v>396</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E223">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>10478</v>
-      </c>
-      <c r="B224" t="s">
+      <c r="C227" t="s">
         <v>399</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D227" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="51">
+      <c r="A228">
+        <v>31740</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E224">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225">
-        <v>24371</v>
-      </c>
-      <c r="B225" t="s">
-        <v>387</v>
-      </c>
-      <c r="C225" t="s">
-        <v>388</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E225">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>7382</v>
-      </c>
-      <c r="B226" t="s">
-        <v>395</v>
-      </c>
-      <c r="C226" t="s">
-        <v>396</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E226">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227">
-        <v>53471</v>
-      </c>
-      <c r="B227" t="s">
+      <c r="C228" t="s">
         <v>401</v>
       </c>
-      <c r="C227" t="s">
+      <c r="D228" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="68">
+      <c r="A229">
+        <v>47313</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E227">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>17790</v>
-      </c>
-      <c r="B228" t="s">
+      <c r="C229" t="s">
         <v>403</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D229" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="51">
+      <c r="A230">
+        <v>15497</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D228" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E228">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229">
-        <v>10613</v>
-      </c>
-      <c r="B229" t="s">
+      <c r="C230" t="s">
         <v>405</v>
       </c>
-      <c r="C229" t="s">
+      <c r="D230" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="34">
+      <c r="A231">
+        <v>20763</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D229" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E229">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230">
-        <v>38864</v>
-      </c>
-      <c r="B230" t="s">
+      <c r="C231" t="s">
         <v>407</v>
       </c>
-      <c r="C230" t="s">
+      <c r="D231" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="119">
+      <c r="A232">
+        <v>42771</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D230" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E230">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A231">
-        <v>31740</v>
-      </c>
-      <c r="B231" t="s">
+      <c r="C232" t="s">
         <v>409</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D232" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="51">
+      <c r="A233">
+        <v>25793</v>
+      </c>
+      <c r="B233" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D231" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E231">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A232">
-        <v>47313</v>
-      </c>
-      <c r="B232" t="s">
+      <c r="C233" t="s">
         <v>411</v>
       </c>
-      <c r="C232" t="s">
+      <c r="D233" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="51">
+      <c r="A234">
+        <v>24855</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E232">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A233">
-        <v>15497</v>
-      </c>
-      <c r="B233" t="s">
+      <c r="C234" t="s">
         <v>413</v>
       </c>
-      <c r="C233" t="s">
+      <c r="D234" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="85">
+      <c r="A235">
+        <v>43814</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D233" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E233">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A234">
-        <v>20763</v>
-      </c>
-      <c r="B234" t="s">
+      <c r="C235" t="s">
         <v>415</v>
       </c>
-      <c r="C234" t="s">
+      <c r="D235" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="51">
+      <c r="A236">
+        <v>55060</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E234">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A235">
-        <v>42771</v>
-      </c>
-      <c r="B235" t="s">
+      <c r="C236" t="s">
         <v>417</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D236" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="51">
+      <c r="A237">
+        <v>13279</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E235">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A236">
-        <v>25793</v>
-      </c>
-      <c r="B236" t="s">
+      <c r="C237" t="s">
         <v>419</v>
       </c>
-      <c r="C236" t="s">
+      <c r="D237" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="34">
+      <c r="A238">
+        <v>13203</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E236">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A237">
-        <v>24855</v>
-      </c>
-      <c r="B237" t="s">
+      <c r="C238" t="s">
         <v>421</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D238" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="34">
+      <c r="A239">
+        <v>7772</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E237">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238">
-        <v>43814</v>
-      </c>
-      <c r="B238" t="s">
+      <c r="C239" t="s">
         <v>423</v>
       </c>
-      <c r="C238" t="s">
+      <c r="D239" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="51">
+      <c r="A240">
+        <v>1368</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E238">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239">
-        <v>55060</v>
-      </c>
-      <c r="B239" t="s">
+      <c r="C240" t="s">
         <v>425</v>
       </c>
-      <c r="C239" t="s">
+      <c r="D240" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="51">
+      <c r="A241">
+        <v>18343</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E239">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240">
-        <v>13279</v>
-      </c>
-      <c r="B240" t="s">
+      <c r="C241" t="s">
         <v>427</v>
       </c>
-      <c r="C240" t="s">
+      <c r="D241" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="34">
+      <c r="A242">
+        <v>44891</v>
+      </c>
+      <c r="B242" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D240" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E240">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241">
-        <v>13203</v>
-      </c>
-      <c r="B241" t="s">
+      <c r="C242" t="s">
         <v>429</v>
       </c>
-      <c r="C241" t="s">
+      <c r="D242" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="68">
+      <c r="A243">
+        <v>1711</v>
+      </c>
+      <c r="B243" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D241" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E241">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242">
-        <v>7772</v>
-      </c>
-      <c r="B242" t="s">
+      <c r="C243" t="s">
         <v>431</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D243" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="68">
+      <c r="A244">
+        <v>1710</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C244" t="s">
+        <v>431</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="51">
+      <c r="A245">
+        <v>18356</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C245" t="s">
+        <v>427</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="34">
+      <c r="A246">
+        <v>51424</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D242" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E242">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243">
-        <v>1368</v>
-      </c>
-      <c r="B243" t="s">
+      <c r="C246" t="s">
         <v>433</v>
       </c>
-      <c r="C243" t="s">
+      <c r="D246" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="34">
+      <c r="A247">
+        <v>51425</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C247" t="s">
+        <v>433</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="51">
+      <c r="A248">
+        <v>1385</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C248" t="s">
+        <v>425</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="51">
+      <c r="A249">
+        <v>55660</v>
+      </c>
+      <c r="B249" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D243" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E243">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244">
-        <v>18343</v>
-      </c>
-      <c r="B244" t="s">
+      <c r="C249" t="s">
         <v>435</v>
       </c>
-      <c r="C244" t="s">
+      <c r="D249" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="51">
+      <c r="A250">
+        <v>13534</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D244" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E244">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245">
-        <v>44891</v>
-      </c>
-      <c r="B245" t="s">
+      <c r="C250" t="s">
         <v>437</v>
       </c>
-      <c r="C245" t="s">
+      <c r="D250" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="51">
+      <c r="A251">
+        <v>20236</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D245" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E245">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246">
-        <v>1711</v>
-      </c>
-      <c r="B246" t="s">
+      <c r="C251" t="s">
         <v>439</v>
       </c>
-      <c r="C246" t="s">
+      <c r="D251" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="51">
+      <c r="A252">
+        <v>45672</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D246" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E246">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247">
-        <v>1710</v>
-      </c>
-      <c r="B247" t="s">
-        <v>439</v>
-      </c>
-      <c r="C247" t="s">
-        <v>440</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E247">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248">
-        <v>18356</v>
-      </c>
-      <c r="B248" t="s">
-        <v>435</v>
-      </c>
-      <c r="C248" t="s">
-        <v>436</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E248">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A249">
-        <v>51424</v>
-      </c>
-      <c r="B249" t="s">
+      <c r="C252" t="s">
         <v>441</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D252" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="51">
+      <c r="A253">
+        <v>45731</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E249">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A250">
-        <v>51425</v>
-      </c>
-      <c r="B250" t="s">
-        <v>441</v>
-      </c>
-      <c r="C250" t="s">
-        <v>442</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E250">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A251">
-        <v>1385</v>
-      </c>
-      <c r="B251" t="s">
-        <v>433</v>
-      </c>
-      <c r="C251" t="s">
-        <v>434</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E251">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A252">
-        <v>55660</v>
-      </c>
-      <c r="B252" t="s">
+      <c r="C253" t="s">
         <v>443</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D253" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="51">
+      <c r="A254">
+        <v>24856</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C254" t="s">
+        <v>413</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="51">
+      <c r="A255">
+        <v>14844</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E252">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A253">
-        <v>13534</v>
-      </c>
-      <c r="B253" t="s">
+      <c r="C255" t="s">
         <v>445</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D255" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="34">
+      <c r="A256">
+        <v>14843</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E253">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A254">
-        <v>20236</v>
-      </c>
-      <c r="B254" t="s">
+      <c r="C256" t="s">
         <v>447</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D256" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E256">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="119">
+      <c r="A257">
+        <v>14821</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D254" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E254">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A255">
-        <v>45672</v>
-      </c>
-      <c r="B255" t="s">
+      <c r="C257" t="s">
         <v>449</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D257" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="51">
+      <c r="A258">
+        <v>28751</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E255">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A256">
-        <v>45731</v>
-      </c>
-      <c r="B256" t="s">
+      <c r="C258" t="s">
         <v>451</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D258" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="51">
+      <c r="A259">
+        <v>28749</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D256" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E256">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257">
-        <v>24856</v>
-      </c>
-      <c r="B257" t="s">
-        <v>421</v>
-      </c>
-      <c r="C257" t="s">
-        <v>422</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E257">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A258">
-        <v>14844</v>
-      </c>
-      <c r="B258" t="s">
+      <c r="C259" t="s">
         <v>453</v>
       </c>
-      <c r="C258" t="s">
+      <c r="D259" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="51">
+      <c r="A260">
+        <v>25394</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E258">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A259">
-        <v>14843</v>
-      </c>
-      <c r="B259" t="s">
+      <c r="C260" t="s">
         <v>455</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D260" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="85">
+      <c r="A261">
+        <v>5212</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E259">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A260">
-        <v>14821</v>
-      </c>
-      <c r="B260" t="s">
+      <c r="C261" t="s">
         <v>457</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D261" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="68">
+      <c r="A262">
+        <v>28627</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E260">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A261">
-        <v>28751</v>
-      </c>
-      <c r="B261" t="s">
+      <c r="C262" t="s">
         <v>459</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D262" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="51">
+      <c r="A263">
+        <v>28386</v>
+      </c>
+      <c r="B263" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D261" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E261">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A262">
-        <v>28749</v>
-      </c>
-      <c r="B262" t="s">
+      <c r="C263" t="s">
         <v>461</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D263" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="34">
+      <c r="A264">
+        <v>2219</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E262">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A263">
-        <v>25394</v>
-      </c>
-      <c r="B263" t="s">
+      <c r="C264" t="s">
         <v>463</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D264" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E264">
+        <v>2</v>
+      </c>
+      <c r="F264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="51">
+      <c r="A265">
+        <v>14240</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E263">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A264">
-        <v>5212</v>
-      </c>
-      <c r="B264" t="s">
+      <c r="C265" t="s">
         <v>465</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D265" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E265">
+        <v>2</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="51">
+      <c r="A266">
+        <v>25828</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D264" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E264">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A265">
-        <v>28627</v>
-      </c>
-      <c r="B265" t="s">
+      <c r="C266" t="s">
         <v>467</v>
       </c>
-      <c r="C265" t="s">
+      <c r="D266" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E266">
+        <v>2</v>
+      </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="17">
+      <c r="A267">
+        <v>35294</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D265" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E265">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A266">
-        <v>28386</v>
-      </c>
-      <c r="B266" t="s">
+      <c r="C267" t="s">
         <v>469</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D267" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E267">
+        <v>2</v>
+      </c>
+      <c r="F267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="51">
+      <c r="A268">
+        <v>28197</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E266">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A267">
-        <v>2219</v>
-      </c>
-      <c r="B267" t="s">
+      <c r="C268" t="s">
         <v>471</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D268" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E268">
+        <v>2</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="51">
+      <c r="A269">
+        <v>25782</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D267" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E267">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A268">
-        <v>14240</v>
-      </c>
-      <c r="B268" t="s">
+      <c r="C269" t="s">
         <v>473</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D269" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E269">
+        <v>2</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="68">
+      <c r="A270">
+        <v>10296</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D268" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E268">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A269">
-        <v>25828</v>
-      </c>
-      <c r="B269" t="s">
+      <c r="C270" t="s">
         <v>475</v>
       </c>
-      <c r="C269" t="s">
+      <c r="D270" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E270">
+        <v>2</v>
+      </c>
+      <c r="F270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="51">
+      <c r="A271">
+        <v>50241</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D269" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E269">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A270">
-        <v>35294</v>
-      </c>
-      <c r="B270" t="s">
+      <c r="C271" t="s">
         <v>477</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D271" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E271">
+        <v>2</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="34">
+      <c r="A272">
+        <v>16463</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D270" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E270">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A271">
-        <v>35296</v>
-      </c>
-      <c r="B271" t="s">
-        <v>477</v>
-      </c>
-      <c r="C271" t="s">
-        <v>478</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E271">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A272">
-        <v>28197</v>
-      </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>479</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E272">
+        <v>2</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="170">
+      <c r="A273">
+        <v>7928</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D272" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E272">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A273">
-        <v>25782</v>
-      </c>
-      <c r="B273" t="s">
+      <c r="C273" t="s">
         <v>481</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E273">
+        <v>2</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="51">
+      <c r="A274">
+        <v>17198</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D273" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E273">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A274">
-        <v>10296</v>
-      </c>
-      <c r="B274" t="s">
+      <c r="C274" t="s">
         <v>483</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E274">
+        <v>2</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="34">
+      <c r="A275">
+        <v>21862</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D274" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E274">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A275">
-        <v>50241</v>
-      </c>
-      <c r="B275" t="s">
+      <c r="C275" t="s">
         <v>485</v>
       </c>
-      <c r="C275" t="s">
+      <c r="D275" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E275">
+        <v>2</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="102">
+      <c r="A276">
+        <v>31330</v>
+      </c>
+      <c r="B276" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D275" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E275">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A276">
-        <v>16463</v>
-      </c>
-      <c r="B276" t="s">
+      <c r="C276" t="s">
         <v>487</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E276">
+        <v>2</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="51">
+      <c r="A277">
+        <v>34201</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D276" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E276">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A277">
-        <v>7928</v>
-      </c>
-      <c r="B277" t="s">
+      <c r="C277" t="s">
         <v>489</v>
       </c>
-      <c r="C277" t="s">
+      <c r="D277" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E277">
+        <v>2</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="51">
+      <c r="A278">
+        <v>52290</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D277" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E277">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A278">
-        <v>17198</v>
-      </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>491</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E278">
+        <v>2</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="51">
+      <c r="A279">
+        <v>9804</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D278" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E278">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A279">
-        <v>21862</v>
-      </c>
-      <c r="B279" t="s">
+      <c r="C279" t="s">
         <v>493</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E279">
+        <v>2</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="102">
+      <c r="A280">
+        <v>31335</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D279" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E279">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A280">
-        <v>31330</v>
-      </c>
-      <c r="B280" t="s">
+      <c r="C280" t="s">
         <v>495</v>
       </c>
-      <c r="C280" t="s">
+      <c r="D280" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E280">
+        <v>2</v>
+      </c>
+      <c r="F280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="34">
+      <c r="A281">
+        <v>22727</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D280" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E280">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A281">
-        <v>34201</v>
-      </c>
-      <c r="B281" t="s">
+      <c r="C281" t="s">
         <v>497</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E281">
+        <v>2</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="102">
+      <c r="A282">
+        <v>31336</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D281" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E281">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A282">
-        <v>52290</v>
-      </c>
-      <c r="B282" t="s">
+      <c r="C282" t="s">
         <v>499</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E282">
+        <v>2</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="51">
+      <c r="A283">
+        <v>9951</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E282">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A283">
-        <v>9804</v>
-      </c>
-      <c r="B283" t="s">
+      <c r="C283" t="s">
         <v>501</v>
       </c>
-      <c r="C283" t="s">
+      <c r="D283" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E283">
+        <v>2</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="51">
+      <c r="A284">
+        <v>9286</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D283" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E283">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A284">
-        <v>31335</v>
-      </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
         <v>503</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E284">
+        <v>2</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="51">
+      <c r="A285">
+        <v>9805</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C285" t="s">
+        <v>493</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E285">
+        <v>2</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="51">
+      <c r="A286">
+        <v>7695</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D284" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E284">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A285">
-        <v>22727</v>
-      </c>
-      <c r="B285" t="s">
+      <c r="C286" t="s">
         <v>505</v>
       </c>
-      <c r="C285" t="s">
+      <c r="D286" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E286">
+        <v>2</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="51">
+      <c r="A287">
+        <v>22164</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C287" t="s">
         <v>506</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E285">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A286">
-        <v>31336</v>
-      </c>
-      <c r="B286" t="s">
+      <c r="D287" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E287">
+        <v>2</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="85">
+      <c r="A288">
+        <v>22814</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C288" t="s">
         <v>507</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D288" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E288">
+        <v>2</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="51">
+      <c r="A289">
+        <v>22471</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C289" t="s">
         <v>508</v>
       </c>
-      <c r="D286" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E286">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A287">
-        <v>9951</v>
-      </c>
-      <c r="B287" t="s">
+      <c r="D289" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E289">
+        <v>2</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="34">
+      <c r="A290">
+        <v>20824</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C290" t="s">
         <v>509</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D290" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E290">
+        <v>2</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="34">
+      <c r="A291">
+        <v>36458</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C291" t="s">
         <v>510</v>
       </c>
-      <c r="D287" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E287">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A288">
-        <v>9286</v>
-      </c>
-      <c r="B288" t="s">
+      <c r="D291" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="51">
+      <c r="A292">
+        <v>22468</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C292" t="s">
+        <v>508</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E292">
+        <v>2</v>
+      </c>
+      <c r="F292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="34">
+      <c r="A293">
+        <v>1043</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C293" t="s">
         <v>512</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E288">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A289">
-        <v>9805</v>
-      </c>
-      <c r="B289" t="s">
-        <v>501</v>
-      </c>
-      <c r="C289" t="s">
-        <v>502</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E289">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A290">
-        <v>7695</v>
-      </c>
-      <c r="B290" t="s">
+      <c r="D293" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E293">
+        <v>2</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="51">
+      <c r="A294">
+        <v>1119</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C294" t="s">
         <v>513</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D294" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E294">
+        <v>2</v>
+      </c>
+      <c r="F294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="51">
+      <c r="A295">
+        <v>5392</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C295" t="s">
         <v>514</v>
       </c>
-      <c r="D290" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E290">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A291">
-        <v>22164</v>
-      </c>
-      <c r="B291" t="s">
-        <v>515</v>
-      </c>
-      <c r="C291" t="s">
-        <v>516</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E291">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A292">
-        <v>22814</v>
-      </c>
-      <c r="B292" t="s">
-        <v>517</v>
-      </c>
-      <c r="C292" t="s">
-        <v>518</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E292">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A293">
-        <v>22471</v>
-      </c>
-      <c r="B293" t="s">
-        <v>519</v>
-      </c>
-      <c r="C293" t="s">
-        <v>520</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E293">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A294">
-        <v>20824</v>
-      </c>
-      <c r="B294" t="s">
-        <v>521</v>
-      </c>
-      <c r="C294" t="s">
-        <v>522</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E294">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A295">
-        <v>36458</v>
-      </c>
-      <c r="B295" t="s">
+      <c r="D295" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E295">
+        <v>2</v>
+      </c>
+      <c r="F295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="34">
+      <c r="A296">
+        <v>16464</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C296" t="s">
+        <v>479</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E296">
+        <v>2</v>
+      </c>
+      <c r="F296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="34">
+      <c r="A297">
+        <v>20825</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C295" t="s">
-        <v>524</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E295">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A296">
-        <v>22468</v>
-      </c>
-      <c r="B296" t="s">
-        <v>519</v>
-      </c>
-      <c r="C296" t="s">
-        <v>520</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E296">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A297">
-        <v>1043</v>
-      </c>
-      <c r="B297" t="s">
-        <v>525</v>
-      </c>
       <c r="C297" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E297">
         <v>2</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A298">
-        <v>1119</v>
-      </c>
-      <c r="B298" t="s">
-        <v>527</v>
-      </c>
-      <c r="C298" t="s">
-        <v>528</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E298">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A299">
-        <v>5392</v>
-      </c>
-      <c r="B299" t="s">
-        <v>529</v>
-      </c>
-      <c r="C299" t="s">
-        <v>530</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E299">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A300">
-        <v>16464</v>
-      </c>
-      <c r="B300" t="s">
-        <v>487</v>
-      </c>
-      <c r="C300" t="s">
-        <v>488</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E300">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A301">
-        <v>20825</v>
-      </c>
-      <c r="B301" t="s">
-        <v>521</v>
-      </c>
-      <c r="C301" t="s">
-        <v>522</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E301">
-        <v>2</v>
+      <c r="F297">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>